--- a/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ23"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.034065</v>
+        <v>0.0562</v>
       </c>
       <c r="E2">
-        <v>0.0929</v>
-      </c>
-      <c r="F2">
-        <v>0.03</v>
+        <v>0.1135</v>
       </c>
       <c r="G2">
-        <v>0.2374553772535582</v>
+        <v>0.3410177583350367</v>
       </c>
       <c r="H2">
-        <v>0.237292503584767</v>
+        <v>0.3407784332113425</v>
       </c>
       <c r="I2">
-        <v>0.3500794266846858</v>
+        <v>0.3203043229512794</v>
       </c>
       <c r="J2">
-        <v>0.3276457211186679</v>
+        <v>0.2918569730734521</v>
       </c>
       <c r="K2">
-        <v>212.484</v>
+        <v>195.548</v>
       </c>
       <c r="L2">
-        <v>0.219038282528088</v>
+        <v>0.2008564347130307</v>
       </c>
       <c r="M2">
-        <v>105.20252</v>
+        <v>75.37599999999999</v>
       </c>
       <c r="N2">
-        <v>0.04981057284574432</v>
+        <v>0.04181749892787735</v>
       </c>
       <c r="O2">
-        <v>0.49510796107001</v>
+        <v>0.3854603473316014</v>
       </c>
       <c r="P2">
-        <v>81.28352</v>
+        <v>75.37599999999999</v>
       </c>
       <c r="Q2">
-        <v>0.0384855675901919</v>
+        <v>0.04181749892787735</v>
       </c>
       <c r="R2">
-        <v>0.3825394853259539</v>
+        <v>0.3854603473316014</v>
       </c>
       <c r="S2">
-        <v>23.919</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2273614738506264</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>152.567</v>
+        <v>141.259</v>
       </c>
       <c r="V2">
-        <v>0.07223638433144638</v>
+        <v>0.07836842073144007</v>
       </c>
       <c r="W2">
-        <v>0.05298295454545455</v>
+        <v>0.01437553300001672</v>
       </c>
       <c r="X2">
-        <v>0.02574437552789642</v>
+        <v>0.05335847850263144</v>
       </c>
       <c r="Y2">
-        <v>0.02723857901755813</v>
+        <v>-0.03898294550261472</v>
       </c>
       <c r="Z2">
-        <v>0.6430125331092026</v>
+        <v>0.6085199074942182</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02615472533381649</v>
+        <v>0.05318382255978003</v>
       </c>
       <c r="AC2">
-        <v>-0.02458241498407822</v>
+        <v>-0.05044018671538921</v>
       </c>
       <c r="AD2">
-        <v>843.196</v>
+        <v>865.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>843.196</v>
+        <v>865.7</v>
       </c>
       <c r="AG2">
-        <v>690.629</v>
+        <v>724.441</v>
       </c>
       <c r="AH2">
-        <v>0.2853215703047595</v>
+        <v>0.3244510623083211</v>
       </c>
       <c r="AI2">
-        <v>0.4679082868770858</v>
+        <v>0.4926789624887885</v>
       </c>
       <c r="AJ2">
-        <v>0.2464172697499287</v>
+        <v>0.286687060238866</v>
       </c>
       <c r="AK2">
-        <v>0.4186932058270238</v>
+        <v>0.4483290415250246</v>
       </c>
       <c r="AL2">
-        <v>42.526</v>
+        <v>49.027</v>
       </c>
       <c r="AM2">
-        <v>41.508</v>
+        <v>44.218</v>
       </c>
       <c r="AN2">
-        <v>2.342002933072616</v>
+        <v>2.674761706137709</v>
       </c>
       <c r="AO2">
-        <v>7.985796924234585</v>
+        <v>6.360556428090644</v>
       </c>
       <c r="AP2">
-        <v>1.918243378366367</v>
+        <v>2.238312400549969</v>
       </c>
       <c r="AQ2">
-        <v>8.181651729787028</v>
+        <v>7.052309014428513</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analizy Online S.A. (WSE:AOL)</t>
+          <t>Fast Finance S.A. (WSE:FFI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,118 +722,103 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0687</v>
+        <v>-0.364</v>
       </c>
       <c r="E3">
-        <v>-0.09519999999999999</v>
+        <v>0.151</v>
       </c>
       <c r="G3">
-        <v>0.06272727272727273</v>
+        <v>0.04016064257028112</v>
       </c>
       <c r="H3">
-        <v>0.06272727272727273</v>
+        <v>0.04016064257028112</v>
       </c>
       <c r="I3">
-        <v>0.1027272727272727</v>
+        <v>4.64524765729585</v>
       </c>
       <c r="J3">
-        <v>0.0858284140102322</v>
+        <v>4.496487460415681</v>
       </c>
       <c r="K3">
-        <v>0.193</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>0.08772727272727272</v>
+        <v>4.28380187416332</v>
       </c>
       <c r="M3">
-        <v>0.302</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03404735062006765</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.564766839378238</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.302</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03404735062006765</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.564766839378238</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.157</v>
+        <v>0.02</v>
       </c>
       <c r="V3">
-        <v>0.01770011273957159</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="W3">
-        <v>0.1939698492462312</v>
+        <v>-0.3312629399585921</v>
       </c>
       <c r="X3">
-        <v>0.02466640972424722</v>
+        <v>0.2629961225524569</v>
       </c>
       <c r="Y3">
-        <v>0.169303439521984</v>
-      </c>
-      <c r="Z3">
-        <v>2.82413350449294</v>
-      </c>
-      <c r="AA3">
-        <v>0.242390899643788</v>
+        <v>-0.594259062511049</v>
       </c>
       <c r="AB3">
-        <v>0.0247345253501794</v>
-      </c>
-      <c r="AC3">
-        <v>0.2176563742936086</v>
+        <v>0.06480615020316392</v>
       </c>
       <c r="AD3">
-        <v>0.097</v>
+        <v>2.57</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.097</v>
+        <v>2.57</v>
       </c>
       <c r="AG3">
-        <v>-0.06</v>
+        <v>2.55</v>
       </c>
       <c r="AH3">
-        <v>0.01081744173079068</v>
+        <v>0.9575260804769002</v>
       </c>
       <c r="AI3">
-        <v>0.1014644351464435</v>
+        <v>-1.152466367713004</v>
       </c>
       <c r="AJ3">
-        <v>-0.006810442678774121</v>
+        <v>0.9572072072072072</v>
       </c>
       <c r="AK3">
-        <v>-0.07509386733416772</v>
+        <v>-1.133333333333333</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.267</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0.2532637075718016</v>
+        <v>0.161</v>
       </c>
       <c r="AO3">
-        <v>226</v>
-      </c>
-      <c r="AP3">
-        <v>-0.1566579634464752</v>
+        <v>12.99625468164794</v>
+      </c>
+      <c r="AQ3">
+        <v>21.5527950310559</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gielda Papierów Wartosciowych w Warszawie S.A. (WSE:GPW)</t>
+          <t>Novina Spólka Akcyjna (WSE:NOV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,124 +838,112 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0587</v>
-      </c>
-      <c r="E4">
-        <v>0.0605</v>
-      </c>
-      <c r="F4">
-        <v>0.03</v>
+        <v>2.516</v>
       </c>
       <c r="G4">
-        <v>0.5801526717557252</v>
+        <v>0.6396396396396395</v>
       </c>
       <c r="H4">
-        <v>0.5801526717557252</v>
+        <v>0.6396396396396395</v>
       </c>
       <c r="I4">
-        <v>0.4742366412213741</v>
+        <v>0.6381381381381381</v>
       </c>
       <c r="J4">
-        <v>0.3896907351249608</v>
+        <v>0.5996187334215504</v>
       </c>
       <c r="K4">
-        <v>42</v>
+        <v>0.466</v>
       </c>
       <c r="L4">
-        <v>0.400763358778626</v>
+        <v>0.6996996996996997</v>
       </c>
       <c r="M4">
-        <v>26.5</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.06177156177156177</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6309523809523809</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>26.5</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.06177156177156177</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6309523809523809</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>82.2</v>
+        <v>0.038</v>
       </c>
       <c r="V4">
-        <v>0.1916083916083916</v>
+        <v>0.01032608695652174</v>
       </c>
       <c r="W4">
-        <v>0.1846965699208443</v>
+        <v>0.2574585635359116</v>
       </c>
       <c r="X4">
-        <v>0.02574437552789642</v>
+        <v>0.05057597835008803</v>
       </c>
       <c r="Y4">
-        <v>0.1589521943929479</v>
+        <v>0.2068825851858236</v>
       </c>
       <c r="Z4">
-        <v>0.5577434805747737</v>
+        <v>0.3739472206625492</v>
       </c>
       <c r="AA4">
-        <v>0.2173474669563379</v>
+        <v>0.2242257588201867</v>
       </c>
       <c r="AB4">
-        <v>0.02561436339566288</v>
+        <v>0.05127075490551002</v>
       </c>
       <c r="AC4">
-        <v>0.191733103560675</v>
+        <v>0.1729550039146767</v>
       </c>
       <c r="AD4">
-        <v>64.90000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>64.90000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="AG4">
-        <v>-17.3</v>
+        <v>0.015</v>
       </c>
       <c r="AH4">
-        <v>0.1314031180400891</v>
+        <v>0.01419769622287704</v>
       </c>
       <c r="AI4">
-        <v>0.2165498832165499</v>
+        <v>0.02036112178255859</v>
       </c>
       <c r="AJ4">
-        <v>-0.04202088899684236</v>
+        <v>0.004059539918809201</v>
       </c>
       <c r="AK4">
-        <v>-0.07954022988505746</v>
+        <v>0.005847953216374269</v>
       </c>
       <c r="AL4">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>4.119000000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="AN4">
-        <v>1.136602451838879</v>
-      </c>
-      <c r="AO4">
-        <v>11.74940898345154</v>
+        <v>0.1244131455399061</v>
       </c>
       <c r="AP4">
-        <v>-0.3029772329246935</v>
+        <v>0.0352112676056338</v>
       </c>
       <c r="AQ4">
-        <v>12.06603544549648</v>
+        <v>-6.746031746031746</v>
       </c>
     </row>
     <row r="5">
@@ -993,121 +963,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.103</v>
+        <v>0.0594</v>
       </c>
       <c r="E5">
-        <v>0.217</v>
+        <v>0.179</v>
       </c>
       <c r="G5">
-        <v>0.5273854633138133</v>
+        <v>0.9766454352441613</v>
       </c>
       <c r="H5">
-        <v>0.5273854633138133</v>
+        <v>0.9766454352441613</v>
       </c>
       <c r="I5">
-        <v>0.918015845676886</v>
+        <v>0.9009200283085632</v>
       </c>
       <c r="J5">
-        <v>0.7528804780138805</v>
+        <v>0.8711923407275803</v>
       </c>
       <c r="K5">
-        <v>154.2</v>
+        <v>162.9</v>
       </c>
       <c r="L5">
-        <v>0.5311746469169824</v>
+        <v>0.5764331210191083</v>
       </c>
       <c r="M5">
-        <v>75.8</v>
+        <v>50.3</v>
       </c>
       <c r="N5">
-        <v>0.04940363683764583</v>
+        <v>0.03677438221962275</v>
       </c>
       <c r="O5">
-        <v>0.4915693904020753</v>
+        <v>0.3087783916513198</v>
       </c>
       <c r="P5">
-        <v>51.9</v>
+        <v>50.3</v>
       </c>
       <c r="Q5">
-        <v>0.03382650068435117</v>
+        <v>0.03677438221962275</v>
       </c>
       <c r="R5">
-        <v>0.3365758754863813</v>
+        <v>0.3087783916513198</v>
       </c>
       <c r="S5">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.3153034300791557</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>44.6</v>
+        <v>39.8</v>
       </c>
       <c r="V5">
-        <v>0.02906863064589715</v>
+        <v>0.02909782131890627</v>
       </c>
       <c r="W5">
-        <v>0.2884399551066217</v>
+        <v>0.2665248691099477</v>
       </c>
       <c r="X5">
-        <v>0.02765611912810577</v>
+        <v>0.05526957916923433</v>
       </c>
       <c r="Y5">
-        <v>0.260783835978516</v>
+        <v>0.2112552899407133</v>
       </c>
       <c r="Z5">
-        <v>0.2835680934612304</v>
+        <v>0.2406027840449534</v>
       </c>
       <c r="AA5">
-        <v>0.2134928817545758</v>
+        <v>0.2096113026176954</v>
       </c>
       <c r="AB5">
-        <v>0.02789599119272729</v>
+        <v>0.05447944465276969</v>
       </c>
       <c r="AC5">
-        <v>0.1855968905618485</v>
+        <v>0.1551318579649258</v>
       </c>
       <c r="AD5">
-        <v>614</v>
+        <v>700.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>614</v>
+        <v>700.6</v>
       </c>
       <c r="AG5">
-        <v>569.4</v>
+        <v>660.8000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.2858073825815761</v>
+        <v>0.3387159156836202</v>
       </c>
       <c r="AI5">
-        <v>0.5011835768508693</v>
+        <v>0.5254631365784144</v>
       </c>
       <c r="AJ5">
-        <v>0.2706659694823407</v>
+        <v>0.3257418909592823</v>
       </c>
       <c r="AK5">
-        <v>0.4823379923761118</v>
+        <v>0.5108620023192888</v>
       </c>
       <c r="AL5">
-        <v>25.2</v>
+        <v>34.7</v>
       </c>
       <c r="AM5">
-        <v>25.147</v>
+        <v>34.45800000000001</v>
       </c>
       <c r="AN5">
-        <v>2.214208438514244</v>
+        <v>2.734582357533177</v>
       </c>
       <c r="AO5">
-        <v>10.57539682539683</v>
+        <v>7.337175792507204</v>
       </c>
       <c r="AP5">
-        <v>2.053371799495131</v>
+        <v>2.579234972677596</v>
       </c>
       <c r="AQ5">
-        <v>10.59768560862131</v>
+        <v>7.388705090254802</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Notoria Serwis S.A. (WSE:NTS)</t>
+          <t>Analizy Online S.A. (WSE:AOL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1127,43 +1097,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06309999999999999</v>
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="E6">
+        <v>-0.0721</v>
       </c>
       <c r="G6">
-        <v>0.2596026490066225</v>
+        <v>0.1859375</v>
       </c>
       <c r="H6">
-        <v>0.2596026490066225</v>
+        <v>0.1859375</v>
       </c>
       <c r="I6">
-        <v>0.07947019867549669</v>
+        <v>0.09739583333333333</v>
       </c>
       <c r="J6">
-        <v>0.07690664387951293</v>
+        <v>0.08090553350970017</v>
       </c>
       <c r="K6">
-        <v>0.12</v>
+        <v>0.156</v>
       </c>
       <c r="L6">
-        <v>0.1589403973509934</v>
+        <v>0.08125</v>
       </c>
       <c r="M6">
-        <v>0.091</v>
+        <v>0.181</v>
       </c>
       <c r="N6">
-        <v>0.03939393939393939</v>
+        <v>0.04725848563968668</v>
       </c>
       <c r="O6">
-        <v>0.7583333333333333</v>
+        <v>1.16025641025641</v>
       </c>
       <c r="P6">
-        <v>0.091</v>
+        <v>0.181</v>
       </c>
       <c r="Q6">
-        <v>0.03939393939393939</v>
+        <v>0.04725848563968668</v>
       </c>
       <c r="R6">
-        <v>0.7583333333333333</v>
+        <v>1.16025641025641</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1172,70 +1145,70 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.129</v>
+        <v>0.183</v>
       </c>
       <c r="V6">
-        <v>0.05584415584415584</v>
+        <v>0.04778067885117494</v>
       </c>
       <c r="W6">
-        <v>0.2127659574468085</v>
+        <v>0.1816065192083818</v>
       </c>
       <c r="X6">
-        <v>0.02462896502127278</v>
+        <v>0.05057312190257749</v>
       </c>
       <c r="Y6">
-        <v>0.1881369924255357</v>
+        <v>0.1310333973058043</v>
       </c>
       <c r="Z6">
-        <v>2.074175824175824</v>
+        <v>2.403003754693367</v>
       </c>
       <c r="AA6">
-        <v>0.1595179014533853</v>
+        <v>0.1944163007992795</v>
       </c>
       <c r="AB6">
-        <v>0.02462972403419069</v>
+        <v>0.0506059851866255</v>
       </c>
       <c r="AC6">
-        <v>0.1348881774191946</v>
+        <v>0.143810315612654</v>
       </c>
       <c r="AD6">
-        <v>0.014</v>
+        <v>0.054</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.014</v>
+        <v>0.054</v>
       </c>
       <c r="AG6">
-        <v>-0.115</v>
+        <v>-0.129</v>
       </c>
       <c r="AH6">
-        <v>0.006024096385542169</v>
+        <v>0.01390319258496396</v>
       </c>
       <c r="AI6">
-        <v>0.02469135802469136</v>
+        <v>0.07317073170731707</v>
       </c>
       <c r="AJ6">
-        <v>-0.05239179954441914</v>
+        <v>-0.03485544447446636</v>
       </c>
       <c r="AK6">
-        <v>-0.2625570776255707</v>
+        <v>-0.2324324324324324</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM6">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.08284023668639053</v>
+        <v>0.169811320754717</v>
+      </c>
+      <c r="AO6">
+        <v>93.5</v>
       </c>
       <c r="AP6">
-        <v>-0.6804733727810651</v>
-      </c>
-      <c r="AQ6">
-        <v>-60</v>
+        <v>-0.4056603773584906</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kredyt Inkaso S.A. (WSE:KRI)</t>
+          <t>Kancelaria Prawna-Inkaso WEC Spólka Akcyjna (WSE:KPI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,118 +1228,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.112</v>
+        <v>0.13</v>
       </c>
       <c r="E7">
-        <v>0.186</v>
+        <v>0.204</v>
       </c>
       <c r="G7">
-        <v>0.3986919104991394</v>
+        <v>0.1583333333333333</v>
       </c>
       <c r="H7">
-        <v>0.3975903614457831</v>
+        <v>0.1583333333333333</v>
       </c>
       <c r="I7">
-        <v>0.4561101549053356</v>
+        <v>0.2259259259259259</v>
       </c>
       <c r="J7">
-        <v>0.3880674924522446</v>
+        <v>0.2259259259259259</v>
       </c>
       <c r="K7">
-        <v>15.5</v>
+        <v>0.286</v>
       </c>
       <c r="L7">
-        <v>0.2667814113597246</v>
+        <v>0.1324074074074074</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>0.08</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02711864406779661</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.2797202797202797</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>0.08</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.02711864406779661</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2797202797202797</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>19.8</v>
+        <v>0.208</v>
       </c>
       <c r="V7">
-        <v>0.3108320251177394</v>
+        <v>0.07050847457627119</v>
       </c>
       <c r="W7">
-        <v>0.2695652173913043</v>
+        <v>0.2288</v>
       </c>
       <c r="X7">
-        <v>0.03725505972520166</v>
+        <v>0.05865421271044877</v>
       </c>
       <c r="Y7">
-        <v>0.2323101576661027</v>
+        <v>0.1701457872895512</v>
       </c>
       <c r="Z7">
-        <v>0.3425101691917704</v>
+        <v>0.8888888888888891</v>
       </c>
       <c r="AA7">
-        <v>0.1329170624976443</v>
+        <v>0.2008230452674897</v>
       </c>
       <c r="AB7">
-        <v>0.031801028567277</v>
+        <v>0.05742537620835794</v>
       </c>
       <c r="AC7">
-        <v>0.1011160339303673</v>
+        <v>0.1433976690591318</v>
       </c>
       <c r="AD7">
-        <v>105.1</v>
+        <v>2.57</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>105.1</v>
+        <v>2.57</v>
       </c>
       <c r="AG7">
-        <v>85.3</v>
+        <v>2.362</v>
       </c>
       <c r="AH7">
-        <v>0.6226303317535544</v>
+        <v>0.4655797101449275</v>
       </c>
       <c r="AI7">
-        <v>0.586823003908431</v>
+        <v>0.6781002638522426</v>
       </c>
       <c r="AJ7">
-        <v>0.5724832214765101</v>
+        <v>0.4446536144578313</v>
       </c>
       <c r="AK7">
-        <v>0.5354676710608913</v>
+        <v>0.6594081518704633</v>
       </c>
       <c r="AL7">
-        <v>7.7</v>
+        <v>0.185</v>
       </c>
       <c r="AM7">
-        <v>7.7</v>
+        <v>0.173</v>
       </c>
       <c r="AN7">
-        <v>3.835766423357664</v>
+        <v>4.876660341555977</v>
       </c>
       <c r="AO7">
-        <v>3.441558441558441</v>
+        <v>2.637837837837838</v>
       </c>
       <c r="AP7">
-        <v>3.113138686131387</v>
+        <v>4.481973434535104</v>
       </c>
       <c r="AQ7">
-        <v>3.441558441558441</v>
+        <v>2.820809248554914</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1353,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kancelaria Prawna-Inkaso WEC Spólka Akcyjna (WSE:KPI)</t>
+          <t>Gielda Papierów Wartosciowych w Warszawie S.A. (WSE:GPW)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,46 +1362,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.009429999999999999</v>
+        <v>0.0348</v>
       </c>
       <c r="E8">
-        <v>0.0157</v>
+        <v>-0.0049</v>
       </c>
       <c r="G8">
-        <v>0.4013793103448275</v>
+        <v>0.6361416361416361</v>
       </c>
       <c r="H8">
-        <v>0.4013793103448275</v>
+        <v>0.6361416361416361</v>
       </c>
       <c r="I8">
-        <v>0.2813793103448276</v>
+        <v>0.3577533577533578</v>
       </c>
       <c r="J8">
-        <v>0.2813793103448276</v>
+        <v>0.2947533845885494</v>
       </c>
       <c r="K8">
-        <v>0.12</v>
+        <v>30</v>
       </c>
       <c r="L8">
-        <v>0.08275862068965517</v>
+        <v>0.3663003663003663</v>
       </c>
       <c r="M8">
-        <v>0.1</v>
+        <v>23.2</v>
       </c>
       <c r="N8">
-        <v>0.03412969283276451</v>
+        <v>0.06813509544787077</v>
       </c>
       <c r="O8">
-        <v>0.8333333333333334</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="P8">
-        <v>0.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q8">
-        <v>0.03412969283276451</v>
+        <v>0.06813509544787077</v>
       </c>
       <c r="R8">
-        <v>0.8333333333333334</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1434,73 +1410,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0.71</v>
+        <v>86.3</v>
       </c>
       <c r="V8">
-        <v>0.242320819112628</v>
+        <v>0.2534508076358297</v>
       </c>
       <c r="W8">
-        <v>0.09523809523809523</v>
+        <v>0.1278227524499361</v>
       </c>
       <c r="X8">
-        <v>0.02953689590528141</v>
+        <v>0.05120167029566908</v>
       </c>
       <c r="Y8">
-        <v>0.06570119933281382</v>
+        <v>0.07662108215426702</v>
       </c>
       <c r="Z8">
-        <v>0.4566929133858268</v>
+        <v>0.4674657534246575</v>
       </c>
       <c r="AA8">
-        <v>0.128503937007874</v>
+        <v>0.137787113001154</v>
       </c>
       <c r="AB8">
-        <v>0.03009618964260464</v>
+        <v>0.05086525664859917</v>
       </c>
       <c r="AC8">
-        <v>0.09840774736526937</v>
+        <v>0.08692185635255487</v>
       </c>
       <c r="AD8">
-        <v>1.89</v>
+        <v>27.5</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.89</v>
+        <v>27.5</v>
       </c>
       <c r="AG8">
-        <v>1.18</v>
+        <v>-58.8</v>
       </c>
       <c r="AH8">
-        <v>0.392116182572614</v>
+        <v>0.07472826086956522</v>
       </c>
       <c r="AI8">
-        <v>0.6</v>
+        <v>0.1249432076328941</v>
       </c>
       <c r="AJ8">
-        <v>0.2871046228710462</v>
+        <v>-0.2087326943556976</v>
       </c>
       <c r="AK8">
-        <v>0.4836065573770492</v>
+        <v>-0.4394618834080717</v>
       </c>
       <c r="AL8">
-        <v>0.126</v>
+        <v>1.11</v>
       </c>
       <c r="AM8">
-        <v>0.11</v>
+        <v>-2.62</v>
       </c>
       <c r="AN8">
-        <v>4.162995594713656</v>
+        <v>0.7703081232492996</v>
       </c>
       <c r="AO8">
-        <v>3.238095238095238</v>
+        <v>26.39639639639639</v>
       </c>
       <c r="AP8">
-        <v>2.599118942731277</v>
+        <v>-1.647058823529411</v>
       </c>
       <c r="AQ8">
-        <v>3.709090909090909</v>
+        <v>-11.18320610687023</v>
       </c>
     </row>
     <row r="9">
@@ -1511,7 +1487,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Novina Alternatywna Spólka Inwestycyjna Spólka Akcyjna (WSE:NOV)</t>
+          <t>Kredyt Inkaso S.A. (WSE:KRI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1520,25 +1496,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.308</v>
+        <v>0.112</v>
+      </c>
+      <c r="E9">
+        <v>0.284</v>
       </c>
       <c r="G9">
-        <v>0.3694117647058824</v>
+        <v>0.001069609507640068</v>
       </c>
       <c r="H9">
-        <v>0.3694117647058824</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.4376470588235294</v>
+        <v>0.4601018675721562</v>
       </c>
       <c r="J9">
-        <v>0.4304251601630752</v>
+        <v>0.3929269949066214</v>
       </c>
       <c r="K9">
-        <v>0.298</v>
+        <v>17</v>
       </c>
       <c r="L9">
-        <v>0.7011764705882353</v>
+        <v>0.2886247877758913</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1562,70 +1541,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>0.4163701067615658</v>
       </c>
       <c r="W9">
-        <v>0.1773809523809524</v>
+        <v>0.2397743300423131</v>
       </c>
       <c r="X9">
-        <v>0.02458241498407822</v>
+        <v>0.07255198481790737</v>
       </c>
       <c r="Y9">
-        <v>0.1527985373968742</v>
+        <v>0.1672223452244057</v>
       </c>
       <c r="Z9">
-        <v>0.2529761904761905</v>
+        <v>0.3555260457536066</v>
       </c>
       <c r="AA9">
-        <v>0.1088873173031589</v>
+        <v>0.1396957807689986</v>
       </c>
       <c r="AB9">
-        <v>0.02458241498407822</v>
+        <v>0.05880051910001645</v>
       </c>
       <c r="AC9">
-        <v>0.08430490231908067</v>
+        <v>0.08089526166898219</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>54.2</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.7010638297872341</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.5034377387318564</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>0.6585662211421628</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>0.4546979865771812</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>7.97</v>
       </c>
       <c r="AM9">
-        <v>-0.134</v>
+        <v>7.856</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.353571428571429</v>
+      </c>
+      <c r="AO9">
+        <v>3.400250941028859</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.935714285714286</v>
       </c>
       <c r="AQ9">
-        <v>-1.388059701492537</v>
+        <v>3.44959266802444</v>
       </c>
     </row>
     <row r="10">
@@ -1636,7 +1618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indos SA (WSE:INS)</t>
+          <t>Notoria Serwis S.A. (WSE:NTS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1645,46 +1627,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00821</v>
+        <v>0.0582</v>
       </c>
       <c r="E10">
-        <v>0.0929</v>
+        <v>-0.238</v>
       </c>
       <c r="G10">
-        <v>0.7573099415204678</v>
+        <v>0.2444794952681388</v>
       </c>
       <c r="H10">
-        <v>0.7573099415204678</v>
+        <v>0.2444794952681388</v>
       </c>
       <c r="I10">
-        <v>0.5935672514619883</v>
+        <v>0.0946372239747634</v>
       </c>
       <c r="J10">
-        <v>0.450960999266695</v>
+        <v>0.07360672975814932</v>
       </c>
       <c r="K10">
-        <v>0.721</v>
+        <v>0.014</v>
       </c>
       <c r="L10">
-        <v>0.2108187134502924</v>
+        <v>0.0220820189274448</v>
       </c>
       <c r="M10">
-        <v>0.287</v>
+        <v>0.036</v>
       </c>
       <c r="N10">
-        <v>0.05134168157423971</v>
+        <v>0.01714285714285714</v>
       </c>
       <c r="O10">
-        <v>0.3980582524271845</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="P10">
-        <v>0.287</v>
+        <v>0.036</v>
       </c>
       <c r="Q10">
-        <v>0.05134168157423971</v>
+        <v>0.01714285714285714</v>
       </c>
       <c r="R10">
-        <v>0.3980582524271845</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1693,73 +1675,70 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>0.04857142857142856</v>
       </c>
       <c r="W10">
-        <v>0.1032951289398281</v>
+        <v>0.02531645569620253</v>
       </c>
       <c r="X10">
-        <v>0.03602797824384047</v>
+        <v>0.05046263564691175</v>
       </c>
       <c r="Y10">
-        <v>0.0672671506959876</v>
+        <v>-0.02514617995070921</v>
       </c>
       <c r="Z10">
-        <v>0.1923509561304837</v>
+        <v>1.447488584474886</v>
       </c>
       <c r="AA10">
-        <v>0.08674277938650712</v>
+        <v>0.106544901065449</v>
       </c>
       <c r="AB10">
-        <v>0.02928198454690284</v>
+        <v>0.05046851262645993</v>
       </c>
       <c r="AC10">
-        <v>0.05746079483960428</v>
+        <v>0.05607638843898908</v>
       </c>
       <c r="AD10">
-        <v>8.33</v>
+        <v>0.005</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>8.33</v>
+        <v>0.005</v>
       </c>
       <c r="AG10">
-        <v>8.33</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.5984195402298851</v>
+        <v>0.002375296912114014</v>
       </c>
       <c r="AI10">
-        <v>0.5353470437017994</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="AJ10">
-        <v>0.5984195402298851</v>
+        <v>-0.04842735896155766</v>
       </c>
       <c r="AK10">
-        <v>0.5353470437017994</v>
+        <v>-0.3310580204778156</v>
       </c>
       <c r="AL10">
-        <v>0.456</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>0.456</v>
+        <v>-0.001</v>
       </c>
       <c r="AN10">
-        <v>3.874418604651163</v>
-      </c>
-      <c r="AO10">
-        <v>4.451754385964912</v>
+        <v>0.03355704697986577</v>
       </c>
       <c r="AP10">
-        <v>3.874418604651163</v>
+        <v>-0.6510067114093959</v>
       </c>
       <c r="AQ10">
-        <v>4.451754385964912</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="11">
@@ -1770,7 +1749,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pragma Inkaso S.A. (WSE:PRI)</t>
+          <t>Indos SA (WSE:INS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1778,41 +1757,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.0542</v>
+      </c>
+      <c r="E11">
+        <v>0.076</v>
+      </c>
       <c r="G11">
-        <v>0.4466666666666667</v>
+        <v>0.6744444444444444</v>
       </c>
       <c r="H11">
-        <v>0.4466666666666667</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="I11">
-        <v>-0.9743589743589743</v>
+        <v>0.5916666666666667</v>
       </c>
       <c r="J11">
-        <v>-0.9743589743589743</v>
+        <v>0.4574229691876751</v>
       </c>
       <c r="K11">
-        <v>-1.04</v>
+        <v>0.948</v>
       </c>
       <c r="L11">
-        <v>0.5333333333333333</v>
+        <v>0.2633333333333333</v>
       </c>
       <c r="M11">
-        <v>1.70752</v>
+        <v>0.259</v>
       </c>
       <c r="N11">
-        <v>0.4978192419825073</v>
+        <v>0.04850187265917603</v>
       </c>
       <c r="O11">
-        <v>-1.641846153846154</v>
+        <v>0.2732067510548523</v>
       </c>
       <c r="P11">
-        <v>1.70752</v>
+        <v>0.259</v>
       </c>
       <c r="Q11">
-        <v>0.4978192419825073</v>
+        <v>0.04850187265917603</v>
       </c>
       <c r="R11">
-        <v>-1.641846153846154</v>
+        <v>0.2732067510548523</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1821,73 +1806,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>0.3294460641399417</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>-0.12590799031477</v>
+        <v>0.1311203319502074</v>
       </c>
       <c r="X11">
-        <v>0.02937449024162959</v>
+        <v>0.06239361216317568</v>
       </c>
       <c r="Y11">
-        <v>-0.1552824805563996</v>
+        <v>0.06872671978703176</v>
       </c>
       <c r="Z11">
-        <v>-0.0749423520368947</v>
+        <v>0.2313624678663239</v>
       </c>
       <c r="AA11">
-        <v>0.07302075326671792</v>
+        <v>0.1058305070100019</v>
       </c>
       <c r="AB11">
-        <v>0.02998489072313461</v>
+        <v>0.05710688051856305</v>
       </c>
       <c r="AC11">
-        <v>0.04303586254358331</v>
+        <v>0.04872362649143887</v>
       </c>
       <c r="AD11">
-        <v>2.14</v>
+        <v>6.77</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.14</v>
+        <v>6.77</v>
       </c>
       <c r="AG11">
-        <v>1.01</v>
+        <v>6.77</v>
       </c>
       <c r="AH11">
-        <v>0.3842010771992819</v>
+        <v>0.5590421139554087</v>
       </c>
       <c r="AI11">
-        <v>0.1838487972508591</v>
+        <v>0.5022255192878338</v>
       </c>
       <c r="AJ11">
-        <v>0.2274774774774775</v>
+        <v>0.5590421139554087</v>
       </c>
       <c r="AK11">
-        <v>0.09609895337773551</v>
+        <v>0.5022255192878338</v>
       </c>
       <c r="AL11">
-        <v>3.2</v>
+        <v>0.461</v>
       </c>
       <c r="AM11">
-        <v>3.2</v>
+        <v>0.453</v>
       </c>
       <c r="AN11">
-        <v>1.097435897435898</v>
+        <v>2.918103448275862</v>
       </c>
       <c r="AO11">
-        <v>0.5937499999999999</v>
+        <v>4.620390455531453</v>
       </c>
       <c r="AP11">
-        <v>0.5179487179487181</v>
+        <v>2.918103448275862</v>
       </c>
       <c r="AQ11">
-        <v>0.5937499999999999</v>
+        <v>4.701986754966887</v>
       </c>
     </row>
     <row r="12">
@@ -1898,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Atlantis SE (WSE:ATS)</t>
+          <t>NWAI Dom Maklerski S.A. (WSE:NWA)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1906,6 +1891,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.414</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1913,64 +1901,67 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.422680412371134</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.422680412371134</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.045</v>
+        <v>1.52</v>
       </c>
       <c r="L12">
-        <v>0.4639175257731958</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.635</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.1125886524822695</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.4177631578947368</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.635</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.1125886524822695</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.4177631578947368</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>0</v>
+        <v>0.889</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>0.1576241134751773</v>
       </c>
       <c r="W12">
-        <v>0.004601226993865031</v>
+        <v>0.504983388704319</v>
       </c>
       <c r="X12">
-        <v>0.02458241498407822</v>
+        <v>0.05044018671538921</v>
       </c>
       <c r="Y12">
-        <v>-0.01998118799021319</v>
+        <v>0.4545432019889298</v>
       </c>
       <c r="Z12">
-        <v>0.01005493935938634</v>
+        <v>6.717171717171719</v>
       </c>
       <c r="AA12">
-        <v>0.004250025914792164</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.02458241498407822</v>
+        <v>0.05044018671538921</v>
       </c>
       <c r="AC12">
-        <v>-0.02033238906928606</v>
+        <v>-0.05044018671538921</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -1982,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>-0.889</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1991,19 +1982,19 @@
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>-0.187118501368133</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>-0.3597733711048158</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.005</v>
+        <v>-0.068</v>
       </c>
       <c r="AQ12">
-        <v>-8.199999999999999</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -2014,7 +2005,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Femion Technology S.A. (WSE:FEM)</t>
+          <t>Wierzyciel S.A. (WSE:WRL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2023,7 +2014,7 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.24</v>
+        <v>-0.153</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2038,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.978</v>
+        <v>-0.157</v>
       </c>
       <c r="L13">
-        <v>-0.4405405405405405</v>
+        <v>-0.6977777777777777</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2065,31 +2056,31 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.05753262158956109</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>-0.7191176470588234</v>
+        <v>-0.06796536796536796</v>
       </c>
       <c r="X13">
-        <v>0.02458241498407822</v>
+        <v>0.05044018671538921</v>
       </c>
       <c r="Y13">
-        <v>-0.7437000620429016</v>
+        <v>-0.1184055546807572</v>
       </c>
       <c r="Z13">
-        <v>0.3887915936952714</v>
+        <v>0.09740259740259741</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.02458241498407822</v>
+        <v>0.05044018671538921</v>
       </c>
       <c r="AC13">
-        <v>-0.02458241498407822</v>
+        <v>-0.05044018671538921</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2101,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-0.485</v>
+        <v>0</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2110,16 +2101,19 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.06104468219005664</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>-0.949119373776908</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>-0.004</v>
+      </c>
+      <c r="AQ13">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2130,7 +2124,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wierzyciel S.A. (WSE:WRL)</t>
+          <t>IDM S.A. (WSE:IDM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2138,9 +2132,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.231</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2154,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>-0.196</v>
+        <v>-0.786</v>
       </c>
       <c r="L14">
-        <v>-0.7747035573122529</v>
+        <v>-3.023076923076923</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2181,64 +2172,67 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>0.05989583333333334</v>
       </c>
       <c r="W14">
-        <v>-0.07596899224806201</v>
+        <v>-1.241706161137441</v>
       </c>
       <c r="X14">
-        <v>0.02458241498407822</v>
+        <v>0.05086864561937011</v>
       </c>
       <c r="Y14">
-        <v>-0.1005514072321402</v>
+        <v>-1.292574806756811</v>
       </c>
       <c r="Z14">
-        <v>0.09806201550387597</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02458241498407822</v>
+        <v>0.05095854489046828</v>
       </c>
       <c r="AC14">
-        <v>-0.02458241498407822</v>
+        <v>-0.05095854489046828</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>-0.111</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.04346743056420475</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.22887323943662</v>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>-0.01466508125247722</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>0.6306818181818182</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.349</v>
       </c>
       <c r="AM14">
-        <v>-0.005</v>
+        <v>0.349</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2249,7 +2243,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NWAI Dom Maklerski S.A. (WSE:NWA)</t>
+          <t>Femion Technology S.A. (WSE:FEM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2258,10 +2252,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.263</v>
-      </c>
-      <c r="E15">
-        <v>0.278</v>
+        <v>-0.409</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2276,91 +2267,88 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0.491</v>
+        <v>-1.31</v>
       </c>
       <c r="L15">
-        <v>0.1309333333333333</v>
+        <v>-2.347670250896057</v>
       </c>
       <c r="M15">
-        <v>0.396</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.0878048780487805</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.8065173116089613</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>0.396</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.0878048780487805</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.8065173116089613</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>2.41</v>
+        <v>0.029</v>
       </c>
       <c r="V15">
-        <v>0.5343680709534369</v>
+        <v>0.006823529411764707</v>
       </c>
       <c r="W15">
-        <v>0.1439882697947214</v>
+        <v>-1.315261044176707</v>
       </c>
       <c r="X15">
-        <v>0.02490940061120103</v>
+        <v>0.05144737783602855</v>
       </c>
       <c r="Y15">
-        <v>0.1190788691835204</v>
+        <v>-1.366708422012735</v>
       </c>
       <c r="Z15">
-        <v>3.068739770867431</v>
+        <v>1.091976516634051</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02505583010428344</v>
+        <v>0.05188820046679037</v>
       </c>
       <c r="AC15">
-        <v>-0.02505583010428344</v>
+        <v>-0.05188820046679037</v>
       </c>
       <c r="AD15">
-        <v>0.192</v>
+        <v>0.454</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.192</v>
+        <v>0.454</v>
       </c>
       <c r="AG15">
-        <v>-2.218</v>
+        <v>0.425</v>
       </c>
       <c r="AH15">
-        <v>0.04083368779242876</v>
+        <v>0.09651360544217688</v>
       </c>
       <c r="AI15">
-        <v>0.05996252342286072</v>
+        <v>1.845528455284553</v>
       </c>
       <c r="AJ15">
-        <v>-0.9677137870855149</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="AK15">
-        <v>-2.800505050505051</v>
+        <v>1.95852534562212</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.038</v>
+        <v>-0.023</v>
       </c>
       <c r="AQ15">
         <v>-0</v>
@@ -2374,7 +2362,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YOLO S.A. (WSE:YOL)</t>
+          <t>Marka S.A. (WSE:MRK)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2383,7 +2371,7 @@
         </is>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>-0.026</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2391,29 +2379,35 @@
       <c r="N16">
         <v>-0</v>
       </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
       <c r="P16">
         <v>-0</v>
       </c>
       <c r="Q16">
         <v>-0</v>
       </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>0.008303571428571429</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>-0</v>
+        <v>0.003434610303830911</v>
       </c>
       <c r="X16">
-        <v>0.0255493673191957</v>
+        <v>0.2144816473044596</v>
       </c>
       <c r="Y16">
-        <v>-0.0255493673191957</v>
+        <v>-0.2110470370006287</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2422,39 +2416,45 @@
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02615472533381649</v>
+        <v>0.06462793144365031</v>
       </c>
       <c r="AC16">
-        <v>-0.02615472533381649</v>
+        <v>-0.06462793144365031</v>
       </c>
       <c r="AD16">
-        <v>1.41</v>
+        <v>6.42</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.41</v>
+        <v>6.42</v>
       </c>
       <c r="AG16">
-        <v>1.317</v>
+        <v>6.42</v>
       </c>
       <c r="AH16">
-        <v>0.1118160190325139</v>
+        <v>0.9456473707467963</v>
       </c>
       <c r="AI16">
-        <v>3.038793103448276</v>
+        <v>20.06249999999998</v>
       </c>
       <c r="AJ16">
-        <v>0.1052169050091875</v>
+        <v>0.9456473707467963</v>
       </c>
       <c r="AK16">
-        <v>3.549865229110512</v>
+        <v>20.06249999999998</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="AM16">
+        <v>0.055</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
         <v>0</v>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marka S.A. (WSE:MRK)</t>
+          <t>Pragma Inkaso S.A. (WSE:PRI)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2474,104 +2474,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D17">
+        <v>-0.339</v>
+      </c>
       <c r="G17">
-        <v>-0</v>
+        <v>-0.09876543209876544</v>
       </c>
       <c r="H17">
-        <v>-0</v>
+        <v>-0.09876543209876544</v>
       </c>
       <c r="I17">
-        <v>-0</v>
+        <v>-0.2263374485596708</v>
       </c>
       <c r="J17">
-        <v>-0</v>
+        <v>-0.1131687242798354</v>
       </c>
       <c r="K17">
-        <v>-0.373</v>
+        <v>-0.457</v>
       </c>
       <c r="L17">
-        <v>0.478818998716303</v>
+        <v>-0.470164609053498</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.2555970149253731</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-1.49890590809628</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.2555970149253731</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-1.49890590809628</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>0.3444029850746269</v>
       </c>
       <c r="W17">
-        <v>0.05298295454545455</v>
+        <v>-0.04810526315789474</v>
       </c>
       <c r="X17">
-        <v>0.1566979852910911</v>
+        <v>0.05578772323926502</v>
       </c>
       <c r="Y17">
-        <v>-0.1037150307456366</v>
+        <v>-0.1038929863971598</v>
       </c>
       <c r="Z17">
-        <v>-0.4750000000000001</v>
+        <v>0.09248334919124641</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>-0.0104662226450999</v>
       </c>
       <c r="AB17">
-        <v>0.032004237438327</v>
+        <v>0.05586991933738335</v>
       </c>
       <c r="AC17">
-        <v>-0.032004237438327</v>
+        <v>-0.06633614198248325</v>
       </c>
       <c r="AD17">
-        <v>8.050000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>8.050000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AG17">
-        <v>8.050000000000001</v>
+        <v>0.597</v>
       </c>
       <c r="AH17">
-        <v>0.9450575252406669</v>
+        <v>0.3619047619047619</v>
       </c>
       <c r="AI17">
-        <v>16.77083333333332</v>
+        <v>0.2215743440233236</v>
       </c>
       <c r="AJ17">
-        <v>0.9450575252406669</v>
+        <v>0.1821788220933781</v>
       </c>
       <c r="AK17">
-        <v>16.77083333333332</v>
+        <v>0.10055583628095</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="AM17">
-        <v>-0.166</v>
+        <v>-0.271</v>
+      </c>
+      <c r="AN17">
+        <v>-18.09523809523809</v>
+      </c>
+      <c r="AO17">
+        <v>-2.15686274509804</v>
+      </c>
+      <c r="AP17">
+        <v>-7.107142857142857</v>
       </c>
       <c r="AQ17">
-        <v>-0</v>
+        <v>0.8118081180811808</v>
       </c>
     </row>
     <row r="18">
@@ -2590,23 +2605,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G18">
-        <v>-0</v>
-      </c>
-      <c r="H18">
-        <v>-0</v>
-      </c>
-      <c r="I18">
-        <v>-0</v>
-      </c>
-      <c r="J18">
-        <v>-0</v>
-      </c>
       <c r="K18">
-        <v>-0.188</v>
-      </c>
-      <c r="L18">
-        <v>2.984126984126984</v>
+        <v>-0.423</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2630,61 +2630,61 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.271</v>
+        <v>0.005</v>
       </c>
       <c r="V18">
-        <v>0.1449197860962567</v>
+        <v>0.005827505827505828</v>
       </c>
       <c r="W18">
-        <v>-0.1740740740740741</v>
+        <v>-0.4918604651162791</v>
       </c>
       <c r="X18">
-        <v>0.03181136193664609</v>
+        <v>0.06593465903199296</v>
       </c>
       <c r="Y18">
-        <v>-0.2058854360107202</v>
+        <v>-0.557795124148272</v>
       </c>
       <c r="Z18">
-        <v>-0.03031761308950914</v>
+        <v>0</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03360551913726514</v>
+        <v>0.07618400685237792</v>
       </c>
       <c r="AC18">
-        <v>-0.03360551913726514</v>
+        <v>-0.07618400685237792</v>
       </c>
       <c r="AD18">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="AG18">
-        <v>1.489</v>
+        <v>1.405</v>
       </c>
       <c r="AH18">
-        <v>0.4848484848484849</v>
+        <v>0.6216931216931217</v>
       </c>
       <c r="AI18">
-        <v>0.6717557251908397</v>
+        <v>0.8407871198568873</v>
       </c>
       <c r="AJ18">
-        <v>0.4432866924679964</v>
+        <v>0.6208572691117985</v>
       </c>
       <c r="AK18">
-        <v>0.633886760323542</v>
+        <v>0.8403110047846889</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.044</v>
+        <v>-0.016</v>
       </c>
       <c r="AQ18">
         <v>-0</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DITIX S.A. (WSE:DTX)</t>
+          <t>BVT S.A. (WSE:BVT)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2706,23 +2706,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D19">
+        <v>-0.148</v>
+      </c>
       <c r="G19">
-        <v>-0.1229508196721311</v>
+        <v>-0.2407766990291262</v>
       </c>
       <c r="H19">
-        <v>-0.1229508196721311</v>
+        <v>-0.2407766990291262</v>
       </c>
       <c r="I19">
-        <v>-0.6311475409836066</v>
+        <v>-0.07378640776699029</v>
       </c>
       <c r="J19">
-        <v>-0.6311475409836066</v>
+        <v>-0.07378640776699029</v>
       </c>
       <c r="K19">
-        <v>-0.051</v>
+        <v>-0.132</v>
       </c>
       <c r="L19">
-        <v>-0.4180327868852459</v>
+        <v>-0.2563106796116505</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2746,73 +2749,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>0.002631578947368421</v>
       </c>
       <c r="W19">
-        <v>-0.07931570762052877</v>
+        <v>-0.4313725490196079</v>
       </c>
       <c r="X19">
-        <v>0.02458241498407822</v>
+        <v>0.05887625887701602</v>
       </c>
       <c r="Y19">
-        <v>-0.103898122604607</v>
+        <v>-0.4902488078966239</v>
       </c>
       <c r="Z19">
-        <v>0.1897356143079316</v>
+        <v>0.2563464410154306</v>
       </c>
       <c r="AA19">
-        <v>-0.119751166407465</v>
+        <v>-0.01891488302638129</v>
       </c>
       <c r="AB19">
-        <v>0.02458241498407822</v>
+        <v>0.05752503520242104</v>
       </c>
       <c r="AC19">
-        <v>-0.1443335813915432</v>
+        <v>-0.07643991822880233</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.017</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>0.7786259541984732</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>0.4714881780250348</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>0.7781178270849273</v>
       </c>
       <c r="AL19">
-        <v>0.003</v>
+        <v>0.102</v>
       </c>
       <c r="AM19">
-        <v>0.003</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="AN19">
-        <v>-0</v>
+        <v>-44.34782608695652</v>
       </c>
       <c r="AO19">
-        <v>-25.66666666666666</v>
+        <v>-0.3725490196078431</v>
       </c>
       <c r="AP19">
-        <v>-0</v>
+        <v>-44.21739130434784</v>
       </c>
       <c r="AQ19">
-        <v>-25.66666666666666</v>
+        <v>-0.3838383838383839</v>
       </c>
     </row>
     <row r="20">
@@ -2823,7 +2826,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fast Finance S.A. (WSE:FFI)</t>
+          <t>DITIX S.A. (WSE:DTX)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2832,28 +2835,25 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.314</v>
-      </c>
-      <c r="E20">
-        <v>-0.237</v>
+        <v>0.0298</v>
       </c>
       <c r="G20">
-        <v>0.1547058823529412</v>
+        <v>-0.2978723404255319</v>
       </c>
       <c r="H20">
-        <v>0.1547058823529412</v>
+        <v>-0.2978723404255319</v>
       </c>
       <c r="I20">
-        <v>0.4058823529411765</v>
+        <v>-0.5638297872340425</v>
       </c>
       <c r="J20">
-        <v>0.3324267619861683</v>
+        <v>-0.5638297872340425</v>
       </c>
       <c r="K20">
-        <v>0.621</v>
+        <v>-0.044</v>
       </c>
       <c r="L20">
-        <v>0.3652941176470588</v>
+        <v>-0.4680851063829787</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2862,7 +2862,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2871,79 +2871,73 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0.07199999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="V20">
-        <v>0.3171806167400881</v>
+        <v>0.02901785714285714</v>
       </c>
       <c r="W20">
-        <v>-0.05594594594594595</v>
+        <v>-0.06321839080459771</v>
       </c>
       <c r="X20">
-        <v>0.1653398842807741</v>
+        <v>0.05115574640767005</v>
       </c>
       <c r="Y20">
-        <v>-0.2212858302267201</v>
+        <v>-0.1143741372122678</v>
       </c>
       <c r="Z20">
-        <v>-0.3519668737060042</v>
+        <v>0.1452859350850078</v>
       </c>
       <c r="AA20">
-        <v>-0.1170032081524816</v>
+        <v>-0.08191653786707884</v>
       </c>
       <c r="AB20">
-        <v>0.03791639940329723</v>
+        <v>0.05128138399975911</v>
       </c>
       <c r="AC20">
-        <v>-0.1549196075557788</v>
+        <v>-0.1331979218668379</v>
       </c>
       <c r="AD20">
-        <v>4.16</v>
+        <v>0.034</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>4.16</v>
+        <v>0.034</v>
       </c>
       <c r="AG20">
-        <v>4.088</v>
+        <v>0.021</v>
       </c>
       <c r="AH20">
-        <v>0.9482562115340779</v>
+        <v>0.07053941908713694</v>
       </c>
       <c r="AI20">
-        <v>-0.7563636363636363</v>
+        <v>0.05362776025236594</v>
       </c>
       <c r="AJ20">
-        <v>0.9473928157589803</v>
+        <v>0.04477611940298508</v>
       </c>
       <c r="AK20">
-        <v>-0.7336683417085427</v>
+        <v>0.03381642512077295</v>
       </c>
       <c r="AL20">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>6.020260492040522</v>
-      </c>
-      <c r="AO20">
-        <v>25.55555555555555</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="AP20">
-        <v>5.916063675832128</v>
-      </c>
-      <c r="AQ20">
-        <v>-2.653846153846154</v>
+        <v>-0.7500000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2954,7 +2948,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BVT S.A. (WSE:BVT)</t>
+          <t>Aforti Holding S.A. (WSE:AFH)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2963,25 +2957,25 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.181</v>
+        <v>0.79</v>
       </c>
       <c r="G21">
-        <v>-0.2054507337526206</v>
+        <v>0.003684507042253521</v>
       </c>
       <c r="H21">
-        <v>-0.2054507337526206</v>
+        <v>0.003492957746478874</v>
       </c>
       <c r="I21">
-        <v>-0.5870020964360588</v>
+        <v>-0.007661971830985916</v>
       </c>
       <c r="J21">
-        <v>-0.5870020964360588</v>
+        <v>-0.007661971830985916</v>
       </c>
       <c r="K21">
-        <v>-0.338</v>
+        <v>-18.2</v>
       </c>
       <c r="L21">
-        <v>-0.7085953878406709</v>
+        <v>-0.03417840375586854</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -3005,73 +2999,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.027</v>
+        <v>0.518</v>
       </c>
       <c r="V21">
-        <v>0.027</v>
+        <v>0.1670967741935484</v>
       </c>
       <c r="W21">
-        <v>-0.3943990665110852</v>
+        <v>-1.189542483660131</v>
       </c>
       <c r="X21">
-        <v>0.03787012310126703</v>
+        <v>0.1976472447767178</v>
       </c>
       <c r="Y21">
-        <v>-0.4322691896123522</v>
+        <v>-1.387189728436848</v>
       </c>
       <c r="Z21">
-        <v>0.2106890459363957</v>
+        <v>14.34536637931034</v>
       </c>
       <c r="AA21">
-        <v>-0.1236749116607774</v>
+        <v>-0.1099137931034483</v>
       </c>
       <c r="AB21">
-        <v>0.03349323564566483</v>
+        <v>0.06164756718803831</v>
       </c>
       <c r="AC21">
-        <v>-0.1571681473064422</v>
+        <v>-0.1715613602914866</v>
       </c>
       <c r="AD21">
-        <v>1.73</v>
+        <v>48.4</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.73</v>
+        <v>48.4</v>
       </c>
       <c r="AG21">
-        <v>1.703</v>
+        <v>47.882</v>
       </c>
       <c r="AH21">
-        <v>0.6336996336996337</v>
+        <v>0.9398058252427184</v>
       </c>
       <c r="AI21">
-        <v>0.849705304518664</v>
+        <v>1.531645569620253</v>
       </c>
       <c r="AJ21">
-        <v>0.6300406955234924</v>
+        <v>0.9391942254128908</v>
       </c>
       <c r="AK21">
-        <v>0.8476854156296666</v>
+        <v>1.54050575896017</v>
       </c>
       <c r="AL21">
-        <v>0.107</v>
+        <v>3.48</v>
       </c>
       <c r="AM21">
-        <v>0.099</v>
+        <v>3.436</v>
       </c>
       <c r="AN21">
-        <v>-6.50375939849624</v>
+        <v>29.1566265060241</v>
       </c>
       <c r="AO21">
-        <v>-2.616822429906542</v>
+        <v>-1.172413793103448</v>
       </c>
       <c r="AP21">
-        <v>-6.402255639097744</v>
+        <v>28.84457831325301</v>
       </c>
       <c r="AQ21">
-        <v>-2.828282828282828</v>
+        <v>-1.187427240977881</v>
       </c>
     </row>
     <row r="22">
@@ -3082,7 +3076,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aforti Holding S.A. (WSE:AFH)</t>
+          <t>Fundusz Hipoteczny DOM S.A. (WSE:FHD)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3090,38 +3084,17 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D22">
-        <v>1.057</v>
-      </c>
-      <c r="E22">
-        <v>0.374</v>
-      </c>
-      <c r="G22">
-        <v>-0.01584327764518695</v>
-      </c>
-      <c r="H22">
-        <v>-0.01603023070803501</v>
-      </c>
-      <c r="I22">
-        <v>-0.01286793953858393</v>
-      </c>
-      <c r="J22">
-        <v>-0.01286793953858393</v>
-      </c>
       <c r="K22">
-        <v>0.996</v>
-      </c>
-      <c r="L22">
-        <v>0.00198090692124105</v>
+        <v>0.593</v>
       </c>
       <c r="M22">
-        <v>0.016</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.001311475409836066</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.01606425702811245</v>
+        <v>-0</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3133,192 +3106,76 @@
         <v>-0</v>
       </c>
       <c r="S22">
-        <v>0.016</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>0.48</v>
+        <v>0.068</v>
       </c>
       <c r="V22">
-        <v>0.03934426229508197</v>
+        <v>0.003238095238095238</v>
       </c>
       <c r="W22">
-        <v>0.06552631578947368</v>
+        <v>0.08824404761904762</v>
       </c>
       <c r="X22">
-        <v>0.04309177813414697</v>
+        <v>0.05047206419815121</v>
       </c>
       <c r="Y22">
-        <v>0.02243453765532671</v>
+        <v>0.03777198342089641</v>
       </c>
       <c r="Z22">
-        <v>10.8429837614026</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>-0.139526859459576</v>
+        <v>-0.2270029673590505</v>
       </c>
       <c r="AB22">
-        <v>0.03452016909618728</v>
+        <v>0.05049074092771016</v>
       </c>
       <c r="AC22">
-        <v>-0.1740470285557633</v>
+        <v>-0.2774937082867607</v>
       </c>
       <c r="AD22">
-        <v>29.4</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>29.4</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AG22">
-        <v>28.92</v>
+        <v>0.002999999999999989</v>
       </c>
       <c r="AH22">
-        <v>0.7067307692307693</v>
+        <v>0.003369560058848654</v>
       </c>
       <c r="AI22">
-        <v>0.6901408450704226</v>
+        <v>0.01171423857449266</v>
       </c>
       <c r="AJ22">
-        <v>0.7033073929961089</v>
+        <v>0.0001428367376089125</v>
       </c>
       <c r="AK22">
-        <v>0.6866096866096866</v>
+        <v>0.0005005840146837958</v>
       </c>
       <c r="AL22">
-        <v>1.25</v>
+        <v>0.244</v>
       </c>
       <c r="AM22">
-        <v>1.101</v>
+        <v>0.244</v>
       </c>
       <c r="AN22">
-        <v>-5.203539823008849</v>
+        <v>-0.04701986754966887</v>
       </c>
       <c r="AO22">
-        <v>-5.176</v>
+        <v>-6.270491803278689</v>
       </c>
       <c r="AP22">
-        <v>-5.11858407079646</v>
+        <v>-0.00198675496688741</v>
       </c>
       <c r="AQ22">
-        <v>-5.876475930971844</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Fundusz Hipoteczny DOM S.A. (WSE:FHD)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="K23">
-        <v>0.343</v>
-      </c>
-      <c r="M23">
-        <v>0.003</v>
-      </c>
-      <c r="N23">
-        <v>0.0002830188679245283</v>
-      </c>
-      <c r="O23">
-        <v>0.008746355685131196</v>
-      </c>
-      <c r="P23">
-        <v>-0</v>
-      </c>
-      <c r="Q23">
-        <v>-0</v>
-      </c>
-      <c r="R23">
-        <v>-0</v>
-      </c>
-      <c r="S23">
-        <v>0.003</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>0.003</v>
-      </c>
-      <c r="V23">
-        <v>0.0002830188679245283</v>
-      </c>
-      <c r="W23">
-        <v>0.05220700152207002</v>
-      </c>
-      <c r="X23">
-        <v>0.02459908077569646</v>
-      </c>
-      <c r="Y23">
-        <v>0.02760792074637355</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>-0.2835213032581453</v>
-      </c>
-      <c r="AB23">
-        <v>0.02460751674420842</v>
-      </c>
-      <c r="AC23">
-        <v>-0.3081288200023538</v>
-      </c>
-      <c r="AD23">
-        <v>0.023</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0.023</v>
-      </c>
-      <c r="AG23">
-        <v>0.02</v>
-      </c>
-      <c r="AH23">
-        <v>0.002165113433116822</v>
-      </c>
-      <c r="AI23">
-        <v>0.003410944683375352</v>
-      </c>
-      <c r="AJ23">
-        <v>0.001883239171374765</v>
-      </c>
-      <c r="AK23">
-        <v>0.002967359050445104</v>
-      </c>
-      <c r="AL23">
-        <v>0.226</v>
-      </c>
-      <c r="AM23">
-        <v>0.226</v>
-      </c>
-      <c r="AN23">
-        <v>-0.01284916201117318</v>
-      </c>
-      <c r="AO23">
-        <v>-8.008849557522124</v>
-      </c>
-      <c r="AP23">
-        <v>-0.0111731843575419</v>
-      </c>
-      <c r="AQ23">
-        <v>-8.008849557522124</v>
+        <v>-6.270491803278689</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ22"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0562</v>
+        <v>0.0697</v>
       </c>
       <c r="E2">
-        <v>0.1135</v>
+        <v>0.223</v>
       </c>
       <c r="G2">
-        <v>0.3410177583350367</v>
+        <v>0.6106905660746103</v>
       </c>
       <c r="H2">
-        <v>0.3407784332113425</v>
+        <v>0.6099658316205714</v>
       </c>
       <c r="I2">
-        <v>0.3203043229512794</v>
+        <v>0.6843610447902179</v>
       </c>
       <c r="J2">
-        <v>0.2918569730734521</v>
+        <v>0.6347860401850121</v>
       </c>
       <c r="K2">
-        <v>195.548</v>
+        <v>280.182</v>
       </c>
       <c r="L2">
-        <v>0.2008564347130307</v>
+        <v>0.4563090984303392</v>
       </c>
       <c r="M2">
-        <v>75.37599999999999</v>
+        <v>94.152</v>
       </c>
       <c r="N2">
-        <v>0.04181749892787735</v>
+        <v>0.03165736131495463</v>
       </c>
       <c r="O2">
-        <v>0.3854603473316014</v>
+        <v>0.3360387176906439</v>
       </c>
       <c r="P2">
-        <v>75.37599999999999</v>
+        <v>93.84399999999999</v>
       </c>
       <c r="Q2">
-        <v>0.04181749892787735</v>
+        <v>0.03155380039978548</v>
       </c>
       <c r="R2">
-        <v>0.3854603473316014</v>
+        <v>0.3349394322261958</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.003271305973319738</v>
       </c>
       <c r="U2">
-        <v>141.259</v>
+        <v>126.698</v>
       </c>
       <c r="V2">
-        <v>0.07836842073144007</v>
+        <v>0.04260052217565343</v>
       </c>
       <c r="W2">
-        <v>0.01437553300001672</v>
+        <v>0.1535213097713098</v>
       </c>
       <c r="X2">
-        <v>0.05335847850263144</v>
+        <v>0.05310697296769407</v>
       </c>
       <c r="Y2">
-        <v>-0.03898294550261472</v>
+        <v>0.1004143368036157</v>
       </c>
       <c r="Z2">
-        <v>0.6085199074942182</v>
+        <v>0.3789544496526867</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.1409674511700652</v>
       </c>
       <c r="AB2">
-        <v>0.05318382255978003</v>
+        <v>0.05308471994731308</v>
       </c>
       <c r="AC2">
-        <v>-0.05044018671538921</v>
+        <v>0.08584082932126311</v>
       </c>
       <c r="AD2">
-        <v>865.7</v>
+        <v>1254.06</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>865.7</v>
+        <v>1254.06</v>
       </c>
       <c r="AG2">
-        <v>724.441</v>
+        <v>1127.362</v>
       </c>
       <c r="AH2">
-        <v>0.3244510623083211</v>
+        <v>0.2965974520801626</v>
       </c>
       <c r="AI2">
-        <v>0.4926789624887885</v>
+        <v>0.5070033050667583</v>
       </c>
       <c r="AJ2">
-        <v>0.286687060238866</v>
+        <v>0.2748686625265119</v>
       </c>
       <c r="AK2">
-        <v>0.4483290415250246</v>
+        <v>0.4803873567876282</v>
       </c>
       <c r="AL2">
-        <v>49.027</v>
+        <v>81.78800000000001</v>
       </c>
       <c r="AM2">
-        <v>44.218</v>
+        <v>62.03600000000002</v>
       </c>
       <c r="AN2">
-        <v>2.674761706137709</v>
+        <v>2.914934021974855</v>
       </c>
       <c r="AO2">
-        <v>6.360556428090644</v>
+        <v>5.13779527559055</v>
       </c>
       <c r="AP2">
-        <v>2.238312400549969</v>
+        <v>2.620437498111427</v>
       </c>
       <c r="AQ2">
-        <v>7.052309014428513</v>
+        <v>6.773647559481589</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fast Finance S.A. (WSE:FFI)</t>
+          <t>Igoria Trade S.A. (WSE:IGT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.364</v>
+        <v>0.128</v>
       </c>
       <c r="E3">
-        <v>0.151</v>
+        <v>0.399</v>
       </c>
       <c r="G3">
-        <v>0.04016064257028112</v>
+        <v>0.2771739130434783</v>
       </c>
       <c r="H3">
-        <v>0.04016064257028112</v>
+        <v>0.2771739130434783</v>
       </c>
       <c r="I3">
-        <v>4.64524765729585</v>
+        <v>0.1826086956521739</v>
       </c>
       <c r="J3">
-        <v>4.496487460415681</v>
+        <v>0.1826086956521739</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>0.342</v>
       </c>
       <c r="L3">
-        <v>4.28380187416332</v>
+        <v>0.1858695652173913</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,58 +767,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.02</v>
+        <v>6.44</v>
       </c>
       <c r="V3">
-        <v>0.1754385964912281</v>
+        <v>3.203980099502488</v>
       </c>
       <c r="W3">
-        <v>-0.3312629399585921</v>
+        <v>0.2826446280991736</v>
       </c>
       <c r="X3">
-        <v>0.2629961225524569</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="Y3">
-        <v>-0.594259062511049</v>
+        <v>0.2298633284510142</v>
       </c>
       <c r="AB3">
-        <v>0.06480615020316392</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="AD3">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.55</v>
+        <v>-6.44</v>
       </c>
       <c r="AH3">
-        <v>0.9575260804769002</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>-1.152466367713004</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.9572072072072072</v>
+        <v>1.45372460496614</v>
       </c>
       <c r="AK3">
-        <v>-1.133333333333333</v>
+        <v>1.352941176470588</v>
       </c>
       <c r="AL3">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.161</v>
-      </c>
-      <c r="AO3">
-        <v>12.99625468164794</v>
+        <v>-0.005</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-12.15094339622642</v>
       </c>
       <c r="AQ3">
-        <v>21.5527950310559</v>
+        <v>-67.2</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Novina Spólka Akcyjna (WSE:NOV)</t>
+          <t>Analizy Online S.A. (WSE:AOL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,112 +841,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>2.516</v>
+        <v>0.115</v>
+      </c>
+      <c r="E4">
+        <v>0.19</v>
       </c>
       <c r="G4">
-        <v>0.6396396396396395</v>
+        <v>0.1773809523809524</v>
       </c>
       <c r="H4">
-        <v>0.6396396396396395</v>
+        <v>0.1773809523809524</v>
       </c>
       <c r="I4">
-        <v>0.6381381381381381</v>
+        <v>0.1575396825396825</v>
       </c>
       <c r="J4">
-        <v>0.5996187334215504</v>
+        <v>0.1269172149734211</v>
       </c>
       <c r="K4">
-        <v>0.466</v>
+        <v>0.343</v>
       </c>
       <c r="L4">
-        <v>0.6996996996996997</v>
+        <v>0.1361111111111111</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.302</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06317991631799162</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.8804664723032068</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.302</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06317991631799162</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.8804664723032068</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.038</v>
+        <v>0.118</v>
       </c>
       <c r="V4">
-        <v>0.01032608695652174</v>
+        <v>0.02468619246861924</v>
       </c>
       <c r="W4">
-        <v>0.2574585635359116</v>
+        <v>0.5014619883040936</v>
       </c>
       <c r="X4">
-        <v>0.05057597835008803</v>
+        <v>0.05285948377778184</v>
       </c>
       <c r="Y4">
-        <v>0.2068825851858236</v>
+        <v>0.4486025045263118</v>
       </c>
       <c r="Z4">
-        <v>0.3739472206625492</v>
+        <v>4.540540540540539</v>
       </c>
       <c r="AA4">
-        <v>0.2242257588201867</v>
+        <v>0.5762727598793171</v>
       </c>
       <c r="AB4">
-        <v>0.05127075490551002</v>
+        <v>0.05283069109991367</v>
       </c>
       <c r="AC4">
-        <v>0.1729550039146767</v>
+        <v>0.5234420687794035</v>
       </c>
       <c r="AD4">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.053</v>
+        <v>0.033</v>
       </c>
       <c r="AG4">
-        <v>0.015</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.01419769622287704</v>
+        <v>0.006856430500727197</v>
       </c>
       <c r="AI4">
-        <v>0.02036112178255859</v>
+        <v>0.03864168618266979</v>
       </c>
       <c r="AJ4">
-        <v>0.004059539918809201</v>
+        <v>-0.01810436634717785</v>
       </c>
       <c r="AK4">
-        <v>0.005847953216374269</v>
+        <v>-0.1154891304347826</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM4">
-        <v>-0.063</v>
+        <v>-0.011</v>
       </c>
       <c r="AN4">
-        <v>0.1244131455399061</v>
+        <v>0.05861456483126111</v>
+      </c>
+      <c r="AO4">
+        <v>132.3333333333333</v>
       </c>
       <c r="AP4">
-        <v>0.0352112676056338</v>
+        <v>-0.1509769094138544</v>
       </c>
       <c r="AQ4">
-        <v>-6.746031746031746</v>
+        <v>-36.09090909090909</v>
       </c>
     </row>
     <row r="5">
@@ -954,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KRUK Spólka Akcyjna (WSE:KRU)</t>
+          <t>Novina Spólka Akcyjna (WSE:NOV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,121 +975,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0594</v>
-      </c>
-      <c r="E5">
-        <v>0.179</v>
+        <v>2.399</v>
       </c>
       <c r="G5">
-        <v>0.9766454352441613</v>
+        <v>0.4408</v>
       </c>
       <c r="H5">
-        <v>0.9766454352441613</v>
+        <v>0.4408</v>
       </c>
       <c r="I5">
-        <v>0.9009200283085632</v>
+        <v>0.7712</v>
       </c>
       <c r="J5">
-        <v>0.8711923407275803</v>
+        <v>0.6753758661887694</v>
       </c>
       <c r="K5">
-        <v>162.9</v>
+        <v>0.733</v>
       </c>
       <c r="L5">
-        <v>0.5764331210191083</v>
+        <v>0.5864</v>
       </c>
       <c r="M5">
-        <v>50.3</v>
+        <v>0.008</v>
       </c>
       <c r="N5">
-        <v>0.03677438221962275</v>
+        <v>0.001286173633440514</v>
       </c>
       <c r="O5">
-        <v>0.3087783916513198</v>
+        <v>0.01091405184174625</v>
       </c>
       <c r="P5">
-        <v>50.3</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03677438221962275</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3087783916513198</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>39.8</v>
+        <v>0.194</v>
       </c>
       <c r="V5">
-        <v>0.02909782131890627</v>
+        <v>0.03118971061093248</v>
       </c>
       <c r="W5">
-        <v>0.2665248691099477</v>
+        <v>0.304149377593361</v>
       </c>
       <c r="X5">
-        <v>0.05526957916923433</v>
+        <v>0.05312359423182848</v>
       </c>
       <c r="Y5">
-        <v>0.2112552899407133</v>
+        <v>0.2510257833615325</v>
       </c>
       <c r="Z5">
-        <v>0.2406027840449534</v>
+        <v>0.5305602716468591</v>
       </c>
       <c r="AA5">
-        <v>0.2096113026176954</v>
+        <v>0.3583276030288463</v>
       </c>
       <c r="AB5">
-        <v>0.05447944465276969</v>
+        <v>0.05395149867745585</v>
       </c>
       <c r="AC5">
-        <v>0.1551318579649258</v>
+        <v>0.3043761043513904</v>
       </c>
       <c r="AD5">
-        <v>700.6</v>
+        <v>0.188</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>700.6</v>
+        <v>0.188</v>
       </c>
       <c r="AG5">
-        <v>660.8000000000001</v>
+        <v>-0.006000000000000005</v>
       </c>
       <c r="AH5">
-        <v>0.3387159156836202</v>
+        <v>0.02933832709113608</v>
       </c>
       <c r="AI5">
-        <v>0.5254631365784144</v>
+        <v>0.05153508771929825</v>
       </c>
       <c r="AJ5">
-        <v>0.3257418909592823</v>
+        <v>-0.0009655616350177029</v>
       </c>
       <c r="AK5">
-        <v>0.5108620023192888</v>
+        <v>-0.001737116386797917</v>
       </c>
       <c r="AL5">
-        <v>34.7</v>
+        <v>0.003</v>
       </c>
       <c r="AM5">
-        <v>34.45800000000001</v>
+        <v>-0.047</v>
       </c>
       <c r="AN5">
-        <v>2.734582357533177</v>
+        <v>0.194818652849741</v>
       </c>
       <c r="AO5">
-        <v>7.337175792507204</v>
+        <v>321.3333333333333</v>
       </c>
       <c r="AP5">
-        <v>2.579234972677596</v>
+        <v>-0.006217616580310887</v>
       </c>
       <c r="AQ5">
-        <v>7.388705090254802</v>
+        <v>-20.51063829787234</v>
       </c>
     </row>
     <row r="6">
@@ -1088,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analizy Online S.A. (WSE:AOL)</t>
+          <t>Kancelaria Prawna-Inkaso WEC Spólka Akcyjna (WSE:KPI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1097,118 +1106,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08900000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="E6">
-        <v>-0.0721</v>
+        <v>0.0809</v>
       </c>
       <c r="G6">
-        <v>0.1859375</v>
+        <v>0.2389221556886228</v>
       </c>
       <c r="H6">
-        <v>0.1859375</v>
+        <v>0.2389221556886228</v>
       </c>
       <c r="I6">
-        <v>0.09739583333333333</v>
+        <v>0.2934131736526946</v>
       </c>
       <c r="J6">
-        <v>0.08090553350970017</v>
+        <v>0.2934131736526946</v>
       </c>
       <c r="K6">
-        <v>0.156</v>
+        <v>0.359</v>
       </c>
       <c r="L6">
-        <v>0.08125</v>
+        <v>0.1074850299401198</v>
       </c>
       <c r="M6">
-        <v>0.181</v>
+        <v>0.265</v>
       </c>
       <c r="N6">
-        <v>0.04725848563968668</v>
+        <v>0.04468802698145026</v>
       </c>
       <c r="O6">
-        <v>1.16025641025641</v>
+        <v>0.7381615598885795</v>
       </c>
       <c r="P6">
-        <v>0.181</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.04725848563968668</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>1.16025641025641</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.265</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0.183</v>
+        <v>0.71</v>
       </c>
       <c r="V6">
-        <v>0.04778067885117494</v>
+        <v>0.1197301854974705</v>
       </c>
       <c r="W6">
-        <v>0.1816065192083818</v>
+        <v>0.296694214876033</v>
       </c>
       <c r="X6">
-        <v>0.05057312190257749</v>
+        <v>0.06042032340195981</v>
       </c>
       <c r="Y6">
-        <v>0.1310333973058043</v>
+        <v>0.2362738914740732</v>
       </c>
       <c r="Z6">
-        <v>2.403003754693367</v>
+        <v>0.9350503919372901</v>
       </c>
       <c r="AA6">
-        <v>0.1944163007992795</v>
+        <v>0.2743561030235163</v>
       </c>
       <c r="AB6">
-        <v>0.0506059851866255</v>
+        <v>0.05655393143177588</v>
       </c>
       <c r="AC6">
-        <v>0.143810315612654</v>
+        <v>0.2178021715917404</v>
       </c>
       <c r="AD6">
-        <v>0.054</v>
+        <v>4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.054</v>
+        <v>4</v>
       </c>
       <c r="AG6">
-        <v>-0.129</v>
+        <v>3.29</v>
       </c>
       <c r="AH6">
-        <v>0.01390319258496396</v>
+        <v>0.4028197381671702</v>
       </c>
       <c r="AI6">
-        <v>0.07317073170731707</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="AJ6">
-        <v>-0.03485544447446636</v>
+        <v>0.3568329718004339</v>
       </c>
       <c r="AK6">
-        <v>-0.2324324324324324</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="AL6">
-        <v>0.002</v>
+        <v>0.361</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AN6">
-        <v>0.169811320754717</v>
+        <v>3.883495145631068</v>
       </c>
       <c r="AO6">
-        <v>93.5</v>
+        <v>2.714681440443213</v>
       </c>
       <c r="AP6">
-        <v>-0.4056603773584906</v>
+        <v>3.194174757281553</v>
+      </c>
+      <c r="AQ6">
+        <v>2.824207492795389</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kancelaria Prawna-Inkaso WEC Spólka Akcyjna (WSE:KPI)</t>
+          <t>KRUK Spólka Akcyjna (WSE:KRU)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,46 +1240,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.13</v>
+        <v>0.0858</v>
       </c>
       <c r="E7">
-        <v>0.204</v>
+        <v>0.256</v>
       </c>
       <c r="G7">
-        <v>0.1583333333333333</v>
+        <v>0.7787633046122656</v>
       </c>
       <c r="H7">
-        <v>0.1583333333333333</v>
+        <v>0.7787633046122656</v>
       </c>
       <c r="I7">
-        <v>0.2259259259259259</v>
+        <v>0.9166244298023314</v>
       </c>
       <c r="J7">
-        <v>0.2259259259259259</v>
+        <v>0.8232156487413937</v>
       </c>
       <c r="K7">
-        <v>0.286</v>
+        <v>202.6</v>
       </c>
       <c r="L7">
-        <v>0.1324074074074074</v>
+        <v>0.5134313228585909</v>
       </c>
       <c r="M7">
-        <v>0.08</v>
+        <v>66.3</v>
       </c>
       <c r="N7">
-        <v>0.02711864406779661</v>
+        <v>0.02828618968386023</v>
       </c>
       <c r="O7">
-        <v>0.2797202797202797</v>
+        <v>0.3272458045409674</v>
       </c>
       <c r="P7">
-        <v>0.08</v>
+        <v>66.3</v>
       </c>
       <c r="Q7">
-        <v>0.02711864406779661</v>
+        <v>0.02828618968386023</v>
       </c>
       <c r="R7">
-        <v>0.2797202797202797</v>
+        <v>0.3272458045409674</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1276,73 +1288,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.208</v>
+        <v>44.3</v>
       </c>
       <c r="V7">
-        <v>0.07050847457627119</v>
+        <v>0.01890012372541491</v>
       </c>
       <c r="W7">
-        <v>0.2288</v>
+        <v>0.3201643489254109</v>
       </c>
       <c r="X7">
-        <v>0.05865421271044877</v>
+        <v>0.05828838916757891</v>
       </c>
       <c r="Y7">
-        <v>0.1701457872895512</v>
+        <v>0.261875959757832</v>
       </c>
       <c r="Z7">
-        <v>0.8888888888888891</v>
+        <v>0.3062451979418087</v>
       </c>
       <c r="AA7">
-        <v>0.2008230452674897</v>
+        <v>0.2521058392976026</v>
       </c>
       <c r="AB7">
-        <v>0.05742537620835794</v>
+        <v>0.0590294394993358</v>
       </c>
       <c r="AC7">
-        <v>0.1433976690591318</v>
+        <v>0.1930763997982668</v>
       </c>
       <c r="AD7">
-        <v>2.57</v>
+        <v>1139.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.57</v>
+        <v>1139.8</v>
       </c>
       <c r="AG7">
-        <v>2.362</v>
+        <v>1095.5</v>
       </c>
       <c r="AH7">
-        <v>0.4655797101449275</v>
+        <v>0.3271808709131097</v>
       </c>
       <c r="AI7">
-        <v>0.6781002638522426</v>
+        <v>0.5720164609053497</v>
       </c>
       <c r="AJ7">
-        <v>0.4446536144578313</v>
+        <v>0.3185148572425423</v>
       </c>
       <c r="AK7">
-        <v>0.6594081518704633</v>
+        <v>0.5622850690345429</v>
       </c>
       <c r="AL7">
-        <v>0.185</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AM7">
-        <v>0.173</v>
+        <v>66.84</v>
       </c>
       <c r="AN7">
-        <v>4.876660341555977</v>
+        <v>3.128740049409827</v>
       </c>
       <c r="AO7">
-        <v>2.637837837837838</v>
+        <v>5.211815561959654</v>
       </c>
       <c r="AP7">
-        <v>4.481973434535104</v>
+        <v>3.007136975020587</v>
       </c>
       <c r="AQ7">
-        <v>2.820809248554914</v>
+        <v>5.411430281268701</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gielda Papierów Wartosciowych w Warszawie S.A. (WSE:GPW)</t>
+          <t>Indos SA (WSE:INS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1362,46 +1374,43 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0348</v>
-      </c>
-      <c r="E8">
-        <v>-0.0049</v>
+        <v>0.0436</v>
       </c>
       <c r="G8">
-        <v>0.6361416361416361</v>
+        <v>0.9146608315098467</v>
       </c>
       <c r="H8">
-        <v>0.6361416361416361</v>
+        <v>0.9146608315098467</v>
       </c>
       <c r="I8">
-        <v>0.3577533577533578</v>
+        <v>0.9124726477024069</v>
       </c>
       <c r="J8">
-        <v>0.2947533845885494</v>
+        <v>0.719772831970517</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>1.2</v>
       </c>
       <c r="L8">
-        <v>0.3663003663003663</v>
+        <v>0.262582056892779</v>
       </c>
       <c r="M8">
-        <v>23.2</v>
+        <v>0.62</v>
       </c>
       <c r="N8">
-        <v>0.06813509544787077</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="O8">
-        <v>0.7733333333333333</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="P8">
-        <v>23.2</v>
+        <v>0.62</v>
       </c>
       <c r="Q8">
-        <v>0.06813509544787077</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R8">
-        <v>0.7733333333333333</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1410,73 +1419,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>86.3</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>0.2534508076358297</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.1278227524499361</v>
+        <v>0.1788375558867362</v>
       </c>
       <c r="X8">
-        <v>0.05120167029566908</v>
+        <v>0.06993094220045813</v>
       </c>
       <c r="Y8">
-        <v>0.07662108215426702</v>
+        <v>0.1089066136862781</v>
       </c>
       <c r="Z8">
-        <v>0.4674657534246575</v>
+        <v>0.3390207715133531</v>
       </c>
       <c r="AA8">
-        <v>0.137787113001154</v>
+        <v>0.2440179408089958</v>
       </c>
       <c r="AB8">
-        <v>0.05086525664859917</v>
+        <v>0.05711993100980556</v>
       </c>
       <c r="AC8">
-        <v>0.08692185635255487</v>
+        <v>0.1868980097991902</v>
       </c>
       <c r="AD8">
-        <v>27.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>27.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AG8">
-        <v>-58.8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.07472826086956522</v>
+        <v>0.6022808267997148</v>
       </c>
       <c r="AI8">
-        <v>0.1249432076328941</v>
+        <v>0.5053827751196173</v>
       </c>
       <c r="AJ8">
-        <v>-0.2087326943556976</v>
+        <v>0.6022808267997148</v>
       </c>
       <c r="AK8">
-        <v>-0.4394618834080717</v>
+        <v>0.5053827751196173</v>
       </c>
       <c r="AL8">
-        <v>1.11</v>
+        <v>0.775</v>
       </c>
       <c r="AM8">
-        <v>-2.62</v>
+        <v>0.767</v>
       </c>
       <c r="AN8">
-        <v>0.7703081232492996</v>
+        <v>1.960556844547564</v>
       </c>
       <c r="AO8">
-        <v>26.39639639639639</v>
+        <v>5.380645161290323</v>
       </c>
       <c r="AP8">
-        <v>-1.647058823529411</v>
+        <v>1.960556844547564</v>
       </c>
       <c r="AQ8">
-        <v>-11.18320610687023</v>
+        <v>5.436766623207301</v>
       </c>
     </row>
     <row r="9">
@@ -1487,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kredyt Inkaso S.A. (WSE:KRI)</t>
+          <t>Capitea S.A. (WSE:CAP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1495,29 +1504,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.112</v>
-      </c>
-      <c r="E9">
-        <v>0.284</v>
-      </c>
       <c r="G9">
-        <v>0.001069609507640068</v>
+        <v>0.3748441926345609</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.3711048158640227</v>
       </c>
       <c r="I9">
-        <v>0.4601018675721562</v>
+        <v>0.2594900849858357</v>
       </c>
       <c r="J9">
-        <v>0.3929269949066214</v>
+        <v>0.2589751699346889</v>
       </c>
       <c r="K9">
-        <v>17</v>
+        <v>38.2</v>
       </c>
       <c r="L9">
-        <v>0.2886247877758913</v>
+        <v>1.08215297450425</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1541,73 +1544,70 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>11.7</v>
+        <v>22</v>
       </c>
       <c r="V9">
-        <v>0.4163701067615658</v>
+        <v>1.083743842364532</v>
       </c>
       <c r="W9">
-        <v>0.2397743300423131</v>
+        <v>-0.06672489082969432</v>
       </c>
       <c r="X9">
-        <v>0.07255198481790737</v>
+        <v>0.05361811142513051</v>
       </c>
       <c r="Y9">
-        <v>0.1672223452244057</v>
+        <v>-0.1203430022548248</v>
       </c>
       <c r="Z9">
-        <v>0.3555260457536066</v>
+        <v>0.9415844225126705</v>
       </c>
       <c r="AA9">
-        <v>0.1396957807689986</v>
+        <v>0.2438469858280747</v>
       </c>
       <c r="AB9">
-        <v>0.05880051910001645</v>
+        <v>0.05734805091440902</v>
       </c>
       <c r="AC9">
-        <v>0.08089526166898219</v>
+        <v>0.1864989349136657</v>
       </c>
       <c r="AD9">
-        <v>65.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>65.90000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>54.2</v>
+        <v>-20.5</v>
       </c>
       <c r="AH9">
-        <v>0.7010638297872341</v>
+        <v>0.06880733944954129</v>
       </c>
       <c r="AI9">
-        <v>0.5034377387318564</v>
+        <v>0.07936507936507937</v>
       </c>
       <c r="AJ9">
-        <v>0.6585662211421628</v>
+        <v>102.5000000000004</v>
       </c>
       <c r="AK9">
-        <v>0.4546979865771812</v>
+        <v>6.612903225806448</v>
       </c>
       <c r="AL9">
-        <v>7.97</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>7.856</v>
+        <v>-8</v>
       </c>
       <c r="AN9">
-        <v>2.353571428571429</v>
-      </c>
-      <c r="AO9">
-        <v>3.400250941028859</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="AP9">
-        <v>1.935714285714286</v>
+        <v>-2.102564102564103</v>
       </c>
       <c r="AQ9">
-        <v>3.44959266802444</v>
+        <v>-1.145</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Notoria Serwis S.A. (WSE:NTS)</t>
+          <t>Gielda Papierów Wartosciowych w Warszawie S.A. (WSE:GPW)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1627,46 +1627,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0582</v>
+        <v>0.0371</v>
       </c>
       <c r="E10">
-        <v>-0.238</v>
+        <v>-0.0433</v>
       </c>
       <c r="G10">
-        <v>0.2444794952681388</v>
+        <v>0.3894080996884735</v>
       </c>
       <c r="H10">
-        <v>0.2444794952681388</v>
+        <v>0.3894080996884735</v>
       </c>
       <c r="I10">
-        <v>0.0946372239747634</v>
+        <v>0.3063343717549325</v>
       </c>
       <c r="J10">
-        <v>0.07360672975814932</v>
+        <v>0.2563221178747477</v>
       </c>
       <c r="K10">
-        <v>0.014</v>
+        <v>34.1</v>
       </c>
       <c r="L10">
-        <v>0.0220820189274448</v>
+        <v>0.3541017653167186</v>
       </c>
       <c r="M10">
-        <v>0.036</v>
+        <v>25.9</v>
       </c>
       <c r="N10">
-        <v>0.01714285714285714</v>
+        <v>0.05708618029534935</v>
       </c>
       <c r="O10">
-        <v>2.571428571428571</v>
+        <v>0.7595307917888562</v>
       </c>
       <c r="P10">
-        <v>0.036</v>
+        <v>25.9</v>
       </c>
       <c r="Q10">
-        <v>0.01714285714285714</v>
+        <v>0.05708618029534935</v>
       </c>
       <c r="R10">
-        <v>2.571428571428571</v>
+        <v>0.7595307917888562</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1675,70 +1675,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.102</v>
+        <v>34.7</v>
       </c>
       <c r="V10">
-        <v>0.04857142857142856</v>
+        <v>0.07648225699801632</v>
       </c>
       <c r="W10">
-        <v>0.02531645569620253</v>
+        <v>0.1772349272349272</v>
       </c>
       <c r="X10">
-        <v>0.05046263564691175</v>
+        <v>0.05283646368717233</v>
       </c>
       <c r="Y10">
-        <v>-0.02514617995070921</v>
+        <v>0.1243984635477549</v>
       </c>
       <c r="Z10">
-        <v>1.447488584474886</v>
+        <v>0.7208083832335328</v>
       </c>
       <c r="AA10">
-        <v>0.106544901065449</v>
+        <v>0.1847591313722919</v>
       </c>
       <c r="AB10">
-        <v>0.05046851262645993</v>
+        <v>0.052793398628156</v>
       </c>
       <c r="AC10">
-        <v>0.05607638843898908</v>
+        <v>0.1319657327441359</v>
       </c>
       <c r="AD10">
-        <v>0.005</v>
+        <v>2.21</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.005</v>
+        <v>2.21</v>
       </c>
       <c r="AG10">
-        <v>-0.09699999999999999</v>
+        <v>-32.49</v>
       </c>
       <c r="AH10">
-        <v>0.002375296912114014</v>
+        <v>0.004847447961220416</v>
       </c>
       <c r="AI10">
-        <v>0.01265822784810127</v>
+        <v>0.009504967528278353</v>
       </c>
       <c r="AJ10">
-        <v>-0.04842735896155766</v>
+        <v>-0.07713492082334228</v>
       </c>
       <c r="AK10">
-        <v>-0.3310580204778156</v>
+        <v>-0.1642485213083262</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.546</v>
       </c>
       <c r="AM10">
-        <v>-0.001</v>
+        <v>-5.574</v>
       </c>
       <c r="AN10">
-        <v>0.03355704697986577</v>
+        <v>0.06405797101449276</v>
+      </c>
+      <c r="AO10">
+        <v>54.02930402930402</v>
       </c>
       <c r="AP10">
-        <v>-0.6510067114093959</v>
+        <v>-0.9417391304347826</v>
       </c>
       <c r="AQ10">
-        <v>-60</v>
+        <v>-5.292429135270901</v>
       </c>
     </row>
     <row r="11">
@@ -1749,7 +1752,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indos SA (WSE:INS)</t>
+          <t>Kredyt Inkaso S.A. (WSE:KRI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1758,121 +1761,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0542</v>
+        <v>0.109</v>
       </c>
       <c r="E11">
-        <v>0.076</v>
+        <v>0.135</v>
       </c>
       <c r="G11">
-        <v>0.6744444444444444</v>
+        <v>0.2625394045534151</v>
       </c>
       <c r="H11">
-        <v>0.6555555555555556</v>
+        <v>0.2591943957968477</v>
       </c>
       <c r="I11">
-        <v>0.5916666666666667</v>
+        <v>0.3239929947460595</v>
       </c>
       <c r="J11">
-        <v>0.4574229691876751</v>
+        <v>0.312767744986028</v>
       </c>
       <c r="K11">
-        <v>0.948</v>
+        <v>8.16</v>
       </c>
       <c r="L11">
-        <v>0.2633333333333333</v>
+        <v>0.142907180385289</v>
       </c>
       <c r="M11">
-        <v>0.259</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.04850187265917603</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.2732067510548523</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.259</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.04850187265917603</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.2732067510548523</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>0.2609561752988048</v>
       </c>
       <c r="W11">
-        <v>0.1311203319502074</v>
+        <v>0.1257318952234206</v>
       </c>
       <c r="X11">
-        <v>0.06239361216317568</v>
+        <v>0.07391952075167242</v>
       </c>
       <c r="Y11">
-        <v>0.06872671978703176</v>
+        <v>0.0518123744717482</v>
       </c>
       <c r="Z11">
-        <v>0.2313624678663239</v>
+        <v>0.485833404237216</v>
       </c>
       <c r="AA11">
-        <v>0.1058305070100019</v>
+        <v>0.1519530182821594</v>
       </c>
       <c r="AB11">
-        <v>0.05710688051856305</v>
+        <v>0.05747194404944483</v>
       </c>
       <c r="AC11">
-        <v>0.04872362649143887</v>
+        <v>0.0944810742327146</v>
       </c>
       <c r="AD11">
-        <v>6.77</v>
+        <v>93.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>6.77</v>
+        <v>93.7</v>
       </c>
       <c r="AG11">
-        <v>6.77</v>
+        <v>80.60000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.5590421139554087</v>
+        <v>0.6511466296038916</v>
       </c>
       <c r="AI11">
-        <v>0.5022255192878338</v>
+        <v>0.5385057471264368</v>
       </c>
       <c r="AJ11">
-        <v>0.5590421139554087</v>
+        <v>0.6162079510703364</v>
       </c>
       <c r="AK11">
-        <v>0.5022255192878338</v>
+        <v>0.5009322560596644</v>
       </c>
       <c r="AL11">
-        <v>0.461</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AM11">
-        <v>0.453</v>
+        <v>8.41</v>
       </c>
       <c r="AN11">
-        <v>2.918103448275862</v>
+        <v>4.805128205128205</v>
       </c>
       <c r="AO11">
-        <v>4.620390455531453</v>
+        <v>1.903292181069959</v>
       </c>
       <c r="AP11">
-        <v>2.918103448275862</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="AQ11">
-        <v>4.701986754966887</v>
+        <v>2.199762187871582</v>
       </c>
     </row>
     <row r="12">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NWAI Dom Maklerski S.A. (WSE:NWA)</t>
+          <t>DITIX S.A. (WSE:DTX)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1892,76 +1892,76 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.414</v>
+        <v>-0.3779999999999999</v>
+      </c>
+      <c r="E12">
+        <v>-0.105</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1.625</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1.448369565217391</v>
       </c>
       <c r="K12">
-        <v>1.52</v>
+        <v>0.081</v>
       </c>
       <c r="L12">
-        <v>0.2857142857142857</v>
+        <v>1.446428571428571</v>
       </c>
       <c r="M12">
-        <v>0.635</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.1125886524822695</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.4177631578947368</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>0.635</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.1125886524822695</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4177631578947368</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>0.1576241134751773</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.504983388704319</v>
+        <v>0.1298076923076923</v>
       </c>
       <c r="X12">
-        <v>0.05044018671538921</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="Y12">
-        <v>0.4545432019889298</v>
+        <v>0.07702639265953293</v>
       </c>
       <c r="Z12">
-        <v>6.717171717171719</v>
+        <v>0.08974358974358974</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.129981884057971</v>
       </c>
       <c r="AB12">
-        <v>0.05044018671538921</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="AC12">
-        <v>-0.05044018671538921</v>
+        <v>0.07720058440981162</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>-0.889</v>
+        <v>0</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1982,19 +1982,22 @@
         <v>0</v>
       </c>
       <c r="AJ12">
-        <v>-0.187118501368133</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>-0.3597733711048158</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.068</v>
-      </c>
-      <c r="AQ12">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2005,7 +2008,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wierzyciel S.A. (WSE:WRL)</t>
+          <t>AKCEPT Finance S.A. (WSE:AFC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2014,25 +2017,28 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.153</v>
+        <v>-0.376</v>
+      </c>
+      <c r="E13">
+        <v>0.258</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2.213114754098361</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2.213114754098361</v>
       </c>
       <c r="K13">
-        <v>-0.157</v>
+        <v>0.092</v>
       </c>
       <c r="L13">
-        <v>-0.6977777777777777</v>
+        <v>1.508196721311475</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2041,7 +2047,7 @@
         <v>-0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -2050,7 +2056,7 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2062,58 +2068,67 @@
         <v>0</v>
       </c>
       <c r="W13">
-        <v>-0.06796536796536796</v>
+        <v>0.1078546307151231</v>
       </c>
       <c r="X13">
-        <v>0.05044018671538921</v>
+        <v>0.08895791248777184</v>
       </c>
       <c r="Y13">
-        <v>-0.1184055546807572</v>
+        <v>0.01889671822735126</v>
       </c>
       <c r="Z13">
-        <v>0.09740259740259741</v>
+        <v>0.02859821847163619</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.06329113924050633</v>
       </c>
       <c r="AB13">
-        <v>0.05044018671538921</v>
+        <v>0.07307345207415417</v>
       </c>
       <c r="AC13">
-        <v>-0.05044018671538921</v>
+        <v>-0.009782312833647833</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.7615894039735099</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>0.9766454352441614</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>0.7615894039735099</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>0.9766454352441614</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="AM13">
-        <v>-0.004</v>
+        <v>0.098</v>
+      </c>
+      <c r="AN13">
+        <v>10.07299270072992</v>
+      </c>
+      <c r="AO13">
+        <v>1.377551020408163</v>
+      </c>
+      <c r="AP13">
+        <v>10.07299270072992</v>
       </c>
       <c r="AQ13">
-        <v>-0</v>
+        <v>1.377551020408163</v>
       </c>
     </row>
     <row r="14">
@@ -2124,7 +2139,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDM S.A. (WSE:IDM)</t>
+          <t>mPay S.A. (WSE:MPY)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2132,23 +2147,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.283</v>
+      </c>
+      <c r="E14">
+        <v>0.723</v>
+      </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.03034825870646767</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.01517412935323383</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.013681592039801</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.01105051664753158</v>
       </c>
       <c r="K14">
-        <v>-0.786</v>
+        <v>0.042</v>
       </c>
       <c r="L14">
-        <v>-3.023076923076923</v>
+        <v>0.005223880597014926</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2157,7 +2178,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2166,73 +2187,79 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.05989583333333334</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>-1.241706161137441</v>
+        <v>0.01404682274247492</v>
       </c>
       <c r="X14">
-        <v>0.05086864561937011</v>
+        <v>0.05283671914016902</v>
       </c>
       <c r="Y14">
-        <v>-1.292574806756811</v>
+        <v>-0.0387898963976941</v>
       </c>
       <c r="Z14">
-        <v>0.4814814814814815</v>
+        <v>2.65609514370664</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>0.029351223602958</v>
       </c>
       <c r="AB14">
-        <v>0.05095854489046828</v>
+        <v>0.05281637997279735</v>
       </c>
       <c r="AC14">
-        <v>-0.05095854489046828</v>
+        <v>-0.02346515636983936</v>
       </c>
       <c r="AD14">
-        <v>0.349</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.349</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AG14">
-        <v>-0.111</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.04346743056420475</v>
+        <v>0.00486978615286894</v>
       </c>
       <c r="AI14">
-        <v>1.22887323943662</v>
+        <v>0.0198332854268468</v>
       </c>
       <c r="AJ14">
-        <v>-0.01466508125247722</v>
+        <v>0.00486978615286894</v>
       </c>
       <c r="AK14">
-        <v>0.6306818181818182</v>
+        <v>0.0198332854268468</v>
       </c>
       <c r="AL14">
-        <v>0.349</v>
+        <v>0.095</v>
       </c>
       <c r="AM14">
-        <v>0.349</v>
+        <v>0.001000000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>0.4928571428571428</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AP14">
+        <v>0.4928571428571428</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>109.9999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2243,7 +2270,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Femion Technology S.A. (WSE:FEM)</t>
+          <t>LexBono S.A. (WSE:LXB)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2252,25 +2279,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.409</v>
+        <v>-0.219</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-0.1214285714285714</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>-0.1214285714285714</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.05714285714285715</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.05714285714285715</v>
       </c>
       <c r="K15">
-        <v>-1.31</v>
+        <v>-0.135</v>
       </c>
       <c r="L15">
-        <v>-2.347670250896057</v>
+        <v>-0.3214285714285715</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2294,64 +2321,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.029</v>
+        <v>0.075</v>
       </c>
       <c r="V15">
-        <v>0.006823529411764707</v>
+        <v>0.06756756756756756</v>
       </c>
       <c r="W15">
-        <v>-1.315261044176707</v>
+        <v>-0.4655172413793104</v>
       </c>
       <c r="X15">
-        <v>0.05144737783602855</v>
+        <v>0.06604464066573763</v>
       </c>
       <c r="Y15">
-        <v>-1.366708422012735</v>
+        <v>-0.5315618820450481</v>
       </c>
       <c r="Z15">
-        <v>1.091976516634051</v>
+        <v>0.3213465952563121</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.01836266258607498</v>
       </c>
       <c r="AB15">
-        <v>0.05188820046679037</v>
+        <v>0.05783326061234043</v>
       </c>
       <c r="AC15">
-        <v>-0.05188820046679037</v>
+        <v>-0.03947059802626544</v>
       </c>
       <c r="AD15">
-        <v>0.454</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.454</v>
+        <v>1.3</v>
       </c>
       <c r="AG15">
-        <v>0.425</v>
+        <v>1.225</v>
       </c>
       <c r="AH15">
-        <v>0.09651360544217688</v>
+        <v>0.5394190871369294</v>
       </c>
       <c r="AI15">
-        <v>1.845528455284553</v>
+        <v>0.8290816326530612</v>
       </c>
       <c r="AJ15">
-        <v>0.09090909090909091</v>
+        <v>0.524625267665953</v>
       </c>
       <c r="AK15">
-        <v>1.95852534562212</v>
+        <v>0.8204956463496316</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AM15">
-        <v>-0.023</v>
+        <v>0.118</v>
+      </c>
+      <c r="AN15">
+        <v>46.42857142857143</v>
+      </c>
+      <c r="AO15">
+        <v>0.2033898305084746</v>
+      </c>
+      <c r="AP15">
+        <v>43.75</v>
       </c>
       <c r="AQ15">
-        <v>-0</v>
+        <v>0.2033898305084746</v>
       </c>
     </row>
     <row r="16">
@@ -2362,7 +2398,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Marka S.A. (WSE:MRK)</t>
+          <t>NWAI Dom Maklerski S.A. (WSE:NWA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2370,92 +2406,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.347</v>
+      </c>
+      <c r="E16">
+        <v>0.464</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
       <c r="K16">
-        <v>-0.026</v>
+        <v>1.84</v>
+      </c>
+      <c r="L16">
+        <v>0.2991869918699187</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>0.722</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.06224137931034483</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>0.392391304347826</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>0.722</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.06224137931034483</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.392391304347826</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>0.3551724137931035</v>
       </c>
       <c r="W16">
-        <v>0.003434610303830911</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="X16">
-        <v>0.2144816473044596</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="Y16">
-        <v>-0.2110470370006287</v>
+        <v>0.4948377479708883</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.488870902468636</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.06462793144365031</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="AC16">
-        <v>-0.06462793144365031</v>
+        <v>-0.0527812996481594</v>
       </c>
       <c r="AD16">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>6.42</v>
+        <v>-4.12</v>
       </c>
       <c r="AH16">
-        <v>0.9456473707467963</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>20.06249999999998</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.9456473707467963</v>
+        <v>-0.5508021390374332</v>
       </c>
       <c r="AK16">
-        <v>20.06249999999998</v>
+        <v>-4.291666666666667</v>
       </c>
       <c r="AL16">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.055</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -2466,7 +2523,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pragma Inkaso S.A. (WSE:PRI)</t>
+          <t>Wierzyciel S.A. (WSE:WRL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2475,118 +2532,106 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.339</v>
+        <v>-0.0117</v>
       </c>
       <c r="G17">
-        <v>-0.09876543209876544</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>-0.09876543209876544</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.2263374485596708</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-0.1131687242798354</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>-0.457</v>
+        <v>-0.103</v>
       </c>
       <c r="L17">
-        <v>-0.470164609053498</v>
+        <v>-0.2641025641025641</v>
       </c>
       <c r="M17">
-        <v>0.6850000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.2555970149253731</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>-1.49890590809628</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>0.6850000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.2555970149253731</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>-1.49890590809628</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0.923</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>0.3444029850746269</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>-0.04810526315789474</v>
+        <v>-0.06058823529411764</v>
       </c>
       <c r="X17">
-        <v>0.05578772323926502</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="Y17">
-        <v>-0.1038929863971598</v>
+        <v>-0.113369534942277</v>
       </c>
       <c r="Z17">
-        <v>0.09248334919124641</v>
+        <v>0.2294117647058824</v>
       </c>
       <c r="AA17">
-        <v>-0.0104662226450999</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.05586991933738335</v>
+        <v>0.0527812996481594</v>
       </c>
       <c r="AC17">
-        <v>-0.06633614198248325</v>
+        <v>-0.0527812996481594</v>
       </c>
       <c r="AD17">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>0.3619047619047619</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.2215743440233236</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>0.1821788220933781</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>0.10055583628095</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>0.102</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>-0.271</v>
-      </c>
-      <c r="AN17">
-        <v>-18.09523809523809</v>
-      </c>
-      <c r="AO17">
-        <v>-2.15686274509804</v>
-      </c>
-      <c r="AP17">
-        <v>-7.107142857142857</v>
+        <v>-0.025</v>
       </c>
       <c r="AQ17">
-        <v>0.8118081180811808</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2597,7 +2642,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Remedis SA (WSE:REM)</t>
+          <t>Pragma Inkaso S.A. (WSE:PRI)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2605,17 +2650,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.381</v>
+      </c>
+      <c r="G18">
+        <v>-0.2623612512613522</v>
+      </c>
+      <c r="H18">
+        <v>-0.2623612512613522</v>
+      </c>
+      <c r="I18">
+        <v>-0.8113017154389506</v>
+      </c>
+      <c r="J18">
+        <v>-0.8113017154389506</v>
+      </c>
       <c r="K18">
-        <v>-0.423</v>
+        <v>-0.762</v>
+      </c>
+      <c r="L18">
+        <v>-0.768920282542886</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>0.035</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.008495145631067963</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0.04593175853018373</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2627,67 +2690,79 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>0.035</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>0.005</v>
+        <v>0.7</v>
       </c>
       <c r="V18">
-        <v>0.005827505827505828</v>
+        <v>0.1699029126213592</v>
       </c>
       <c r="W18">
-        <v>-0.4918604651162791</v>
+        <v>-0.1424299065420561</v>
       </c>
       <c r="X18">
-        <v>0.06593465903199296</v>
+        <v>0.05467793760285752</v>
       </c>
       <c r="Y18">
-        <v>-0.557795124148272</v>
+        <v>-0.1971078441449136</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>0.1666386413317639</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>-0.1351942155708761</v>
       </c>
       <c r="AB18">
-        <v>0.07618400685237792</v>
+        <v>0.05313934630054011</v>
       </c>
       <c r="AC18">
-        <v>-0.07618400685237792</v>
+        <v>-0.1883335618714162</v>
       </c>
       <c r="AD18">
-        <v>1.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AG18">
-        <v>1.405</v>
+        <v>-0.01000000000000001</v>
       </c>
       <c r="AH18">
-        <v>0.6216931216931217</v>
+        <v>0.1434511434511434</v>
       </c>
       <c r="AI18">
-        <v>0.8407871198568873</v>
+        <v>0.1148086522462562</v>
       </c>
       <c r="AJ18">
-        <v>0.6208572691117985</v>
+        <v>-0.002433090024330902</v>
       </c>
       <c r="AK18">
-        <v>0.8403110047846889</v>
+        <v>-0.001883239171374766</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AM18">
-        <v>-0.016</v>
+        <v>0.04899999999999999</v>
+      </c>
+      <c r="AN18">
+        <v>-1.053435114503817</v>
+      </c>
+      <c r="AO18">
+        <v>-13.6271186440678</v>
+      </c>
+      <c r="AP18">
+        <v>0.0152671755725191</v>
       </c>
       <c r="AQ18">
-        <v>-0</v>
+        <v>-16.40816326530613</v>
       </c>
     </row>
     <row r="19">
@@ -2698,7 +2773,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BVT S.A. (WSE:BVT)</t>
+          <t>Fundusz Hipoteczny DOM S.A. (WSE:FHD)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2706,26 +2781,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D19">
-        <v>-0.148</v>
-      </c>
-      <c r="G19">
-        <v>-0.2407766990291262</v>
-      </c>
-      <c r="H19">
-        <v>-0.2407766990291262</v>
-      </c>
-      <c r="I19">
-        <v>-0.07378640776699029</v>
-      </c>
-      <c r="J19">
-        <v>-0.07378640776699029</v>
-      </c>
       <c r="K19">
-        <v>-0.132</v>
-      </c>
-      <c r="L19">
-        <v>-0.2563106796116505</v>
+        <v>-5.63</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2749,73 +2806,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.003</v>
+        <v>0.111</v>
       </c>
       <c r="V19">
-        <v>0.002631578947368421</v>
+        <v>0.00412639405204461</v>
       </c>
       <c r="W19">
-        <v>-0.4313725490196079</v>
+        <v>-0.9398998330550917</v>
       </c>
       <c r="X19">
-        <v>0.05887625887701602</v>
+        <v>0.0528469753739416</v>
       </c>
       <c r="Y19">
-        <v>-0.4902488078966239</v>
+        <v>-0.9927468084290333</v>
       </c>
       <c r="Z19">
-        <v>0.2563464410154306</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>-0.01891488302638129</v>
+        <v>-0.7892541298181212</v>
       </c>
       <c r="AB19">
-        <v>0.05752503520242104</v>
+        <v>0.05286964991837085</v>
       </c>
       <c r="AC19">
-        <v>-0.07643991822880233</v>
+        <v>-0.842123779736492</v>
       </c>
       <c r="AD19">
-        <v>1.02</v>
+        <v>0.156</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.02</v>
+        <v>0.156</v>
       </c>
       <c r="AG19">
-        <v>1.017</v>
+        <v>0.045</v>
       </c>
       <c r="AH19">
-        <v>0.4722222222222222</v>
+        <v>0.00576581904198699</v>
       </c>
       <c r="AI19">
-        <v>0.7786259541984732</v>
+        <v>0.1194486983154671</v>
       </c>
       <c r="AJ19">
-        <v>0.4714881780250348</v>
+        <v>0.001670068658378178</v>
       </c>
       <c r="AK19">
-        <v>0.7781178270849273</v>
+        <v>0.03765690376569038</v>
       </c>
       <c r="AL19">
-        <v>0.102</v>
+        <v>0.584</v>
       </c>
       <c r="AM19">
-        <v>0.09899999999999999</v>
+        <v>0.582</v>
       </c>
       <c r="AN19">
-        <v>-44.34782608695652</v>
+        <v>-0.03319148936170212</v>
       </c>
       <c r="AO19">
-        <v>-0.3725490196078431</v>
+        <v>-8.099315068493151</v>
       </c>
       <c r="AP19">
-        <v>-44.21739130434784</v>
+        <v>-0.009574468085106383</v>
       </c>
       <c r="AQ19">
-        <v>-0.3838383838383839</v>
+        <v>-8.127147766323025</v>
       </c>
     </row>
     <row r="20">
@@ -2826,7 +2883,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DITIX S.A. (WSE:DTX)</t>
+          <t>Mycodern S.A. (WSE:MCD)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2835,25 +2892,25 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0298</v>
+        <v>0.0536</v>
       </c>
       <c r="G20">
-        <v>-0.2978723404255319</v>
+        <v>-0.006422018348623853</v>
       </c>
       <c r="H20">
-        <v>-0.2978723404255319</v>
+        <v>-0.006422018348623853</v>
       </c>
       <c r="I20">
-        <v>-0.5638297872340425</v>
+        <v>-0.2963302752293578</v>
       </c>
       <c r="J20">
-        <v>-0.5638297872340425</v>
+        <v>-0.2963302752293578</v>
       </c>
       <c r="K20">
-        <v>-0.044</v>
+        <v>-1.28</v>
       </c>
       <c r="L20">
-        <v>-0.4680851063829787</v>
+        <v>-1.174311926605504</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2877,305 +2934,64 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>0.013</v>
+        <v>0.13</v>
       </c>
       <c r="V20">
-        <v>0.02901785714285714</v>
+        <v>0.006074766355140188</v>
       </c>
       <c r="W20">
-        <v>-0.06321839080459771</v>
+        <v>98.46153846153847</v>
       </c>
       <c r="X20">
-        <v>0.05115574640767005</v>
+        <v>0.05309035170355965</v>
       </c>
       <c r="Y20">
-        <v>-0.1143741372122678</v>
-      </c>
-      <c r="Z20">
-        <v>0.1452859350850078</v>
-      </c>
-      <c r="AA20">
-        <v>-0.08191653786707884</v>
+        <v>98.40844810983491</v>
       </c>
       <c r="AB20">
-        <v>0.05128138399975911</v>
-      </c>
-      <c r="AC20">
-        <v>-0.1331979218668379</v>
+        <v>0.05303009359408605</v>
       </c>
       <c r="AD20">
-        <v>0.034</v>
+        <v>0.584</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.034</v>
+        <v>0.584</v>
       </c>
       <c r="AG20">
-        <v>0.021</v>
+        <v>0.454</v>
       </c>
       <c r="AH20">
-        <v>0.07053941908713694</v>
+        <v>0.02656477438136827</v>
       </c>
       <c r="AI20">
-        <v>0.05362776025236594</v>
+        <v>0.1072740631888317</v>
       </c>
       <c r="AJ20">
-        <v>0.04477611940298508</v>
+        <v>0.02077422897410085</v>
       </c>
       <c r="AK20">
-        <v>0.03381642512077295</v>
+        <v>0.08543470079036507</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AN20">
-        <v>-1.214285714285714</v>
+        <v>-2.027777777777778</v>
+      </c>
+      <c r="AO20">
+        <v>-12.42307692307692</v>
       </c>
       <c r="AP20">
-        <v>-0.7500000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Aforti Holding S.A. (WSE:AFH)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>0.79</v>
-      </c>
-      <c r="G21">
-        <v>0.003684507042253521</v>
-      </c>
-      <c r="H21">
-        <v>0.003492957746478874</v>
-      </c>
-      <c r="I21">
-        <v>-0.007661971830985916</v>
-      </c>
-      <c r="J21">
-        <v>-0.007661971830985916</v>
-      </c>
-      <c r="K21">
-        <v>-18.2</v>
-      </c>
-      <c r="L21">
-        <v>-0.03417840375586854</v>
-      </c>
-      <c r="M21">
-        <v>-0</v>
-      </c>
-      <c r="N21">
-        <v>-0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>-0</v>
-      </c>
-      <c r="Q21">
-        <v>-0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0.518</v>
-      </c>
-      <c r="V21">
-        <v>0.1670967741935484</v>
-      </c>
-      <c r="W21">
-        <v>-1.189542483660131</v>
-      </c>
-      <c r="X21">
-        <v>0.1976472447767178</v>
-      </c>
-      <c r="Y21">
-        <v>-1.387189728436848</v>
-      </c>
-      <c r="Z21">
-        <v>14.34536637931034</v>
-      </c>
-      <c r="AA21">
-        <v>-0.1099137931034483</v>
-      </c>
-      <c r="AB21">
-        <v>0.06164756718803831</v>
-      </c>
-      <c r="AC21">
-        <v>-0.1715613602914866</v>
-      </c>
-      <c r="AD21">
-        <v>48.4</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>48.4</v>
-      </c>
-      <c r="AG21">
-        <v>47.882</v>
-      </c>
-      <c r="AH21">
-        <v>0.9398058252427184</v>
-      </c>
-      <c r="AI21">
-        <v>1.531645569620253</v>
-      </c>
-      <c r="AJ21">
-        <v>0.9391942254128908</v>
-      </c>
-      <c r="AK21">
-        <v>1.54050575896017</v>
-      </c>
-      <c r="AL21">
-        <v>3.48</v>
-      </c>
-      <c r="AM21">
-        <v>3.436</v>
-      </c>
-      <c r="AN21">
-        <v>29.1566265060241</v>
-      </c>
-      <c r="AO21">
-        <v>-1.172413793103448</v>
-      </c>
-      <c r="AP21">
-        <v>28.84457831325301</v>
-      </c>
-      <c r="AQ21">
-        <v>-1.187427240977881</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Fundusz Hipoteczny DOM S.A. (WSE:FHD)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="K22">
-        <v>0.593</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>-0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>-0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0.068</v>
-      </c>
-      <c r="V22">
-        <v>0.003238095238095238</v>
-      </c>
-      <c r="W22">
-        <v>0.08824404761904762</v>
-      </c>
-      <c r="X22">
-        <v>0.05047206419815121</v>
-      </c>
-      <c r="Y22">
-        <v>0.03777198342089641</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-      <c r="AA22">
-        <v>-0.2270029673590505</v>
-      </c>
-      <c r="AB22">
-        <v>0.05049074092771016</v>
-      </c>
-      <c r="AC22">
-        <v>-0.2774937082867607</v>
-      </c>
-      <c r="AD22">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AG22">
-        <v>0.002999999999999989</v>
-      </c>
-      <c r="AH22">
-        <v>0.003369560058848654</v>
-      </c>
-      <c r="AI22">
-        <v>0.01171423857449266</v>
-      </c>
-      <c r="AJ22">
-        <v>0.0001428367376089125</v>
-      </c>
-      <c r="AK22">
-        <v>0.0005005840146837958</v>
-      </c>
-      <c r="AL22">
-        <v>0.244</v>
-      </c>
-      <c r="AM22">
-        <v>0.244</v>
-      </c>
-      <c r="AN22">
-        <v>-0.04701986754966887</v>
-      </c>
-      <c r="AO22">
-        <v>-6.270491803278689</v>
-      </c>
-      <c r="AP22">
-        <v>-0.00198675496688741</v>
-      </c>
-      <c r="AQ22">
-        <v>-6.270491803278689</v>
+        <v>-1.576388888888889</v>
+      </c>
+      <c r="AQ20">
+        <v>-12.42307692307692</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.112</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="E2">
-        <v>0.32</v>
+        <v>0.20945</v>
       </c>
       <c r="G2">
-        <v>0.7970691893897236</v>
+        <v>0.6545361327823385</v>
       </c>
       <c r="H2">
-        <v>0.7970691893897236</v>
+        <v>0.6537677050324604</v>
       </c>
       <c r="I2">
-        <v>0.9590057503246151</v>
+        <v>0.7577167071264879</v>
       </c>
       <c r="J2">
-        <v>0.9590057503246151</v>
+        <v>0.6938515436415895</v>
       </c>
       <c r="K2">
-        <v>308.7</v>
+        <v>382.96</v>
       </c>
       <c r="L2">
-        <v>0.5726210350584306</v>
+        <v>0.4731142943621864</v>
       </c>
       <c r="M2">
-        <v>90.5</v>
+        <v>126.382</v>
       </c>
       <c r="N2">
-        <v>0.04641263654546387</v>
+        <v>0.05056831435884529</v>
       </c>
       <c r="O2">
-        <v>0.2931648850016197</v>
+        <v>0.3300135784416127</v>
       </c>
       <c r="P2">
-        <v>90.5</v>
+        <v>126.056</v>
       </c>
       <c r="Q2">
-        <v>0.04641263654546387</v>
+        <v>0.05043787433984746</v>
       </c>
       <c r="R2">
-        <v>0.2931648850016197</v>
+        <v>0.3291623146020472</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.002579481255242044</v>
       </c>
       <c r="U2">
-        <v>46.4</v>
+        <v>179.856</v>
       </c>
       <c r="V2">
-        <v>0.02379609210728755</v>
+        <v>0.07196447870206579</v>
       </c>
       <c r="W2">
-        <v>0.3619416109743229</v>
+        <v>0.1370499419279907</v>
       </c>
       <c r="X2">
-        <v>0.06723566410556206</v>
+        <v>0.06104509693283117</v>
       </c>
       <c r="Y2">
-        <v>0.2947059468687608</v>
+        <v>0.07600484499515955</v>
       </c>
       <c r="Z2">
-        <v>0.2772477847434006</v>
+        <v>0.337810654591741</v>
       </c>
       <c r="AA2">
-        <v>0.2658822198336822</v>
+        <v>0.1212960355859568</v>
       </c>
       <c r="AB2">
-        <v>0.06486977160439247</v>
+        <v>0.05943693725639897</v>
       </c>
       <c r="AC2">
-        <v>0.2010124482292897</v>
+        <v>0.0602354834381981</v>
       </c>
       <c r="AD2">
-        <v>1537.2</v>
+        <v>1767.21</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1537.2</v>
+        <v>1767.21</v>
       </c>
       <c r="AG2">
-        <v>1490.8</v>
+        <v>1587.354</v>
       </c>
       <c r="AH2">
-        <v>0.4408247540936595</v>
+        <v>0.4142115574964906</v>
       </c>
       <c r="AI2">
-        <v>0.5725992699098561</v>
+        <v>0.5259841610373902</v>
       </c>
       <c r="AJ2">
-        <v>0.4332839247827477</v>
+        <v>0.3884302475390833</v>
       </c>
       <c r="AK2">
-        <v>0.5650822530513229</v>
+        <v>0.4991742034491</v>
       </c>
       <c r="AL2">
-        <v>118.1</v>
+        <v>134.985</v>
       </c>
       <c r="AM2">
-        <v>109.44</v>
+        <v>116.041</v>
       </c>
       <c r="AN2">
-        <v>2.9527468305801</v>
+        <v>2.821175940958703</v>
       </c>
       <c r="AO2">
-        <v>4.377646062658764</v>
+        <v>4.543690039634035</v>
       </c>
       <c r="AP2">
-        <v>2.863618901267768</v>
+        <v>2.534053629497661</v>
       </c>
       <c r="AQ2">
-        <v>4.724049707602339</v>
+        <v>5.28545944967727</v>
       </c>
     </row>
     <row r="3">
@@ -713,130 +713,2148 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Analizy Online S.A. (WSE:AOL)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.769</v>
+      </c>
+      <c r="G3">
+        <v>0.1869158878504673</v>
+      </c>
+      <c r="H3">
+        <v>0.1869158878504673</v>
+      </c>
+      <c r="I3">
+        <v>0.2071651090342679</v>
+      </c>
+      <c r="J3">
+        <v>0.1625852754446153</v>
+      </c>
+      <c r="K3">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.1735202492211838</v>
+      </c>
+      <c r="M3">
+        <v>0.468</v>
+      </c>
+      <c r="N3">
+        <v>0.08880455407969641</v>
+      </c>
+      <c r="O3">
+        <v>0.8402154398563734</v>
+      </c>
+      <c r="P3">
+        <v>0.468</v>
+      </c>
+      <c r="Q3">
+        <v>0.08880455407969641</v>
+      </c>
+      <c r="R3">
+        <v>0.8402154398563734</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0.111</v>
+      </c>
+      <c r="V3">
+        <v>0.02106261859582543</v>
+      </c>
+      <c r="W3">
+        <v>0.6784409257003655</v>
+      </c>
+      <c r="X3">
+        <v>0.05891683758725972</v>
+      </c>
+      <c r="Y3">
+        <v>0.6195240881131058</v>
+      </c>
+      <c r="Z3">
+        <v>4.361413043478261</v>
+      </c>
+      <c r="AA3">
+        <v>0.7091015410016511</v>
+      </c>
+      <c r="AB3">
+        <v>0.05888910548205262</v>
+      </c>
+      <c r="AC3">
+        <v>0.6502124355195985</v>
+      </c>
+      <c r="AD3">
+        <v>0.02</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.02</v>
+      </c>
+      <c r="AG3">
+        <v>-0.091</v>
+      </c>
+      <c r="AH3">
+        <v>0.003780718336483932</v>
+      </c>
+      <c r="AI3">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.01757095964471906</v>
+      </c>
+      <c r="AK3">
+        <v>-0.09795479009687835</v>
+      </c>
+      <c r="AL3">
+        <v>0.002</v>
+      </c>
+      <c r="AM3">
+        <v>-0.004</v>
+      </c>
+      <c r="AN3">
+        <v>0.02466091245376079</v>
+      </c>
+      <c r="AO3">
+        <v>332.5</v>
+      </c>
+      <c r="AP3">
+        <v>-0.1122071516646116</v>
+      </c>
+      <c r="AQ3">
+        <v>-166.25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NOVINA pozyczkihipoteczne.eu S.A. (WSE:NOV)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1.397</v>
+      </c>
+      <c r="E4">
+        <v>0.903</v>
+      </c>
+      <c r="G4">
+        <v>0.5915492957746479</v>
+      </c>
+      <c r="H4">
+        <v>0.5915492957746479</v>
+      </c>
+      <c r="I4">
+        <v>0.7511737089201879</v>
+      </c>
+      <c r="J4">
+        <v>0.662627534293283</v>
+      </c>
+      <c r="K4">
+        <v>1.58</v>
+      </c>
+      <c r="L4">
+        <v>0.7417840375586855</v>
+      </c>
+      <c r="M4">
+        <v>0.058</v>
+      </c>
+      <c r="N4">
+        <v>0.006946107784431138</v>
+      </c>
+      <c r="O4">
+        <v>0.03670886075949367</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0.058</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>0.067</v>
+      </c>
+      <c r="V4">
+        <v>0.008023952095808385</v>
+      </c>
+      <c r="W4">
+        <v>0.4566473988439307</v>
+      </c>
+      <c r="X4">
+        <v>0.05897050986241244</v>
+      </c>
+      <c r="Y4">
+        <v>0.3976768889815183</v>
+      </c>
+      <c r="Z4">
+        <v>0.6166763173132599</v>
+      </c>
+      <c r="AA4">
+        <v>0.4086267075983477</v>
+      </c>
+      <c r="AB4">
+        <v>0.05905146876037303</v>
+      </c>
+      <c r="AC4">
+        <v>0.3495752388379746</v>
+      </c>
+      <c r="AD4">
+        <v>0.074</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.074</v>
+      </c>
+      <c r="AG4">
+        <v>0.006999999999999992</v>
+      </c>
+      <c r="AH4">
+        <v>0.008784425451092117</v>
+      </c>
+      <c r="AI4">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="AJ4">
+        <v>0.0008376211559171943</v>
+      </c>
+      <c r="AK4">
+        <v>0.001049947502624868</v>
+      </c>
+      <c r="AL4">
+        <v>0.005</v>
+      </c>
+      <c r="AM4">
+        <v>-0.164</v>
+      </c>
+      <c r="AN4">
+        <v>0.04512195121951219</v>
+      </c>
+      <c r="AO4">
+        <v>320</v>
+      </c>
+      <c r="AP4">
+        <v>0.004268292682926825</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.75609756097561</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Capitea S.A. (WSE:CAP)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.4713438735177865</v>
+      </c>
+      <c r="H5">
+        <v>0.4683794466403162</v>
+      </c>
+      <c r="I5">
+        <v>0.5928853754940712</v>
+      </c>
+      <c r="J5">
+        <v>0.5906593798604473</v>
+      </c>
+      <c r="K5">
+        <v>27.5</v>
+      </c>
+      <c r="L5">
+        <v>0.5434782608695652</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>24.1</v>
+      </c>
+      <c r="V5">
+        <v>2.317307692307693</v>
+      </c>
+      <c r="W5">
+        <v>1.580459770114943</v>
+      </c>
+      <c r="X5">
+        <v>0.1457520518521316</v>
+      </c>
+      <c r="Y5">
+        <v>1.434707718262811</v>
+      </c>
+      <c r="Z5">
+        <v>0.584295612009238</v>
+      </c>
+      <c r="AA5">
+        <v>0.3451196838445569</v>
+      </c>
+      <c r="AB5">
+        <v>0.0636204021691586</v>
+      </c>
+      <c r="AC5">
+        <v>0.2814992816753983</v>
+      </c>
+      <c r="AD5">
+        <v>85.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>85.3</v>
+      </c>
+      <c r="AG5">
+        <v>61.2</v>
+      </c>
+      <c r="AH5">
+        <v>0.8913270637408568</v>
+      </c>
+      <c r="AI5">
+        <v>0.6602167182662539</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8547486033519553</v>
+      </c>
+      <c r="AK5">
+        <v>0.582302568981922</v>
+      </c>
+      <c r="AL5">
+        <v>0.154</v>
+      </c>
+      <c r="AM5">
+        <v>-1.166</v>
+      </c>
+      <c r="AN5">
+        <v>2.769480519480519</v>
+      </c>
+      <c r="AO5">
+        <v>194.8051948051948</v>
+      </c>
+      <c r="AP5">
+        <v>1.987012987012987</v>
+      </c>
+      <c r="AQ5">
+        <v>-25.72898799313893</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>KRUK Spólka Akcyjna (WSE:KRU)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>0.112</v>
       </c>
-      <c r="E3">
+      <c r="E6">
         <v>0.32</v>
       </c>
-      <c r="G3">
+      <c r="G6">
         <v>0.7970691893897236</v>
       </c>
-      <c r="H3">
+      <c r="H6">
         <v>0.7970691893897236</v>
       </c>
-      <c r="I3">
+      <c r="I6">
         <v>0.9590057503246151</v>
       </c>
-      <c r="J3">
+      <c r="J6">
         <v>0.9590057503246151</v>
       </c>
-      <c r="K3">
+      <c r="K6">
         <v>308.7</v>
       </c>
-      <c r="L3">
+      <c r="L6">
         <v>0.5726210350584306</v>
       </c>
-      <c r="M3">
+      <c r="M6">
         <v>90.5</v>
       </c>
-      <c r="N3">
+      <c r="N6">
         <v>0.04641263654546387</v>
       </c>
-      <c r="O3">
+      <c r="O6">
         <v>0.2931648850016197</v>
       </c>
-      <c r="P3">
+      <c r="P6">
         <v>90.5</v>
       </c>
-      <c r="Q3">
+      <c r="Q6">
         <v>0.04641263654546387</v>
       </c>
-      <c r="R3">
+      <c r="R6">
         <v>0.2931648850016197</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
         <v>46.4</v>
       </c>
-      <c r="V3">
+      <c r="V6">
         <v>0.02379609210728755</v>
       </c>
-      <c r="W3">
+      <c r="W6">
         <v>0.3619416109743229</v>
       </c>
-      <c r="X3">
-        <v>0.06723566410556206</v>
-      </c>
-      <c r="Y3">
-        <v>0.2947059468687608</v>
-      </c>
-      <c r="Z3">
+      <c r="X6">
+        <v>0.06722688501017826</v>
+      </c>
+      <c r="Y6">
+        <v>0.2947147259641446</v>
+      </c>
+      <c r="Z6">
         <v>0.2772477847434006</v>
       </c>
-      <c r="AA3">
+      <c r="AA6">
         <v>0.2658822198336822</v>
       </c>
-      <c r="AB3">
-        <v>0.06486977160439247</v>
-      </c>
-      <c r="AC3">
-        <v>0.2010124482292897</v>
-      </c>
-      <c r="AD3">
+      <c r="AB6">
+        <v>0.06486486255157239</v>
+      </c>
+      <c r="AC6">
+        <v>0.2010173572821098</v>
+      </c>
+      <c r="AD6">
         <v>1537.2</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>1537.2</v>
       </c>
-      <c r="AG3">
+      <c r="AG6">
         <v>1490.8</v>
       </c>
-      <c r="AH3">
+      <c r="AH6">
         <v>0.4408247540936595</v>
       </c>
-      <c r="AI3">
+      <c r="AI6">
         <v>0.5725992699098561</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ6">
         <v>0.4332839247827477</v>
       </c>
-      <c r="AK3">
+      <c r="AK6">
         <v>0.5650822530513229</v>
       </c>
-      <c r="AL3">
+      <c r="AL6">
         <v>118.1</v>
       </c>
-      <c r="AM3">
+      <c r="AM6">
         <v>109.44</v>
       </c>
-      <c r="AN3">
+      <c r="AN6">
         <v>2.9527468305801</v>
       </c>
-      <c r="AO3">
+      <c r="AO6">
         <v>4.377646062658764</v>
       </c>
-      <c r="AP3">
+      <c r="AP6">
         <v>2.863618901267768</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ6">
         <v>4.724049707602339</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kancelaria Prawna-Inkaso WEC Spólka Akcyjna (WSE:KPI)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.133</v>
+      </c>
+      <c r="E7">
+        <v>-0.0539</v>
+      </c>
+      <c r="G7">
+        <v>0.3053221288515406</v>
+      </c>
+      <c r="H7">
+        <v>0.3053221288515406</v>
+      </c>
+      <c r="I7">
+        <v>0.3221288515406162</v>
+      </c>
+      <c r="J7">
+        <v>0.3221288515406162</v>
+      </c>
+      <c r="K7">
+        <v>0.262</v>
+      </c>
+      <c r="L7">
+        <v>0.07338935574229692</v>
+      </c>
+      <c r="M7">
+        <v>0.287</v>
+      </c>
+      <c r="N7">
+        <v>0.04922813036020584</v>
+      </c>
+      <c r="O7">
+        <v>1.095419847328244</v>
+      </c>
+      <c r="P7">
+        <v>0.019</v>
+      </c>
+      <c r="Q7">
+        <v>0.003259005145797599</v>
+      </c>
+      <c r="R7">
+        <v>0.07251908396946564</v>
+      </c>
+      <c r="S7">
+        <v>0.268</v>
+      </c>
+      <c r="T7">
+        <v>0.9337979094076655</v>
+      </c>
+      <c r="U7">
+        <v>0.096</v>
+      </c>
+      <c r="V7">
+        <v>0.01646655231560892</v>
+      </c>
+      <c r="W7">
+        <v>0.1523255813953489</v>
+      </c>
+      <c r="X7">
+        <v>0.06736120357000364</v>
+      </c>
+      <c r="Y7">
+        <v>0.08496437782534522</v>
+      </c>
+      <c r="Z7">
+        <v>0.7125748502994012</v>
+      </c>
+      <c r="AA7">
+        <v>0.2295409181636726</v>
+      </c>
+      <c r="AB7">
+        <v>0.06034307962021225</v>
+      </c>
+      <c r="AC7">
+        <v>0.1691978385434604</v>
+      </c>
+      <c r="AD7">
+        <v>4.67</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>4.67</v>
+      </c>
+      <c r="AG7">
+        <v>4.574</v>
+      </c>
+      <c r="AH7">
+        <v>0.4447619047619047</v>
+      </c>
+      <c r="AI7">
+        <v>0.6738816738816739</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4396386005382545</v>
+      </c>
+      <c r="AK7">
+        <v>0.6693005560433128</v>
+      </c>
+      <c r="AL7">
+        <v>0.609</v>
+      </c>
+      <c r="AM7">
+        <v>0.575</v>
+      </c>
+      <c r="AN7">
+        <v>3.859504132231405</v>
+      </c>
+      <c r="AO7">
+        <v>1.888341543513957</v>
+      </c>
+      <c r="AP7">
+        <v>3.780165289256198</v>
+      </c>
+      <c r="AQ7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Notoria Serwis S.A. (WSE:NTS)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0643</v>
+      </c>
+      <c r="E8">
+        <v>0.0989</v>
+      </c>
+      <c r="G8">
+        <v>0.2583783783783783</v>
+      </c>
+      <c r="H8">
+        <v>0.2583783783783783</v>
+      </c>
+      <c r="I8">
+        <v>0.07567567567567568</v>
+      </c>
+      <c r="J8">
+        <v>0.07567567567567568</v>
+      </c>
+      <c r="K8">
+        <v>0.079</v>
+      </c>
+      <c r="L8">
+        <v>0.08540540540540541</v>
+      </c>
+      <c r="M8">
+        <v>0.06</v>
+      </c>
+      <c r="N8">
+        <v>0.02489626556016597</v>
+      </c>
+      <c r="O8">
+        <v>0.7594936708860759</v>
+      </c>
+      <c r="P8">
+        <v>0.06</v>
+      </c>
+      <c r="Q8">
+        <v>0.02489626556016597</v>
+      </c>
+      <c r="R8">
+        <v>0.7594936708860759</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0.135</v>
+      </c>
+      <c r="V8">
+        <v>0.05601659751037345</v>
+      </c>
+      <c r="W8">
+        <v>0.138353765323993</v>
+      </c>
+      <c r="X8">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="Y8">
+        <v>0.07947712537755536</v>
+      </c>
+      <c r="Z8">
+        <v>2.306733167082295</v>
+      </c>
+      <c r="AA8">
+        <v>0.174563591022444</v>
+      </c>
+      <c r="AB8">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="AC8">
+        <v>0.1156869510760063</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>-0.135</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.05934065934065934</v>
+      </c>
+      <c r="AK8">
+        <v>-0.3</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.001</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>-0.52734375</v>
+      </c>
+      <c r="AQ8">
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gielda Papierów Wartosciowych w Warszawie S.A. (WSE:GPW)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0629</v>
+      </c>
+      <c r="E9">
+        <v>0.0112</v>
+      </c>
+      <c r="G9">
+        <v>0.321546052631579</v>
+      </c>
+      <c r="H9">
+        <v>0.321546052631579</v>
+      </c>
+      <c r="I9">
+        <v>0.2689144736842106</v>
+      </c>
+      <c r="J9">
+        <v>0.2248035548200022</v>
+      </c>
+      <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>0.3289473684210527</v>
+      </c>
+      <c r="M9">
+        <v>32.8</v>
+      </c>
+      <c r="N9">
+        <v>0.0798442064264849</v>
+      </c>
+      <c r="O9">
+        <v>0.82</v>
+      </c>
+      <c r="P9">
+        <v>32.8</v>
+      </c>
+      <c r="Q9">
+        <v>0.0798442064264849</v>
+      </c>
+      <c r="R9">
+        <v>0.82</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>50.7</v>
+      </c>
+      <c r="V9">
+        <v>0.1234177215189873</v>
+      </c>
+      <c r="W9">
+        <v>0.1756697408871322</v>
+      </c>
+      <c r="X9">
+        <v>0.05907362991392678</v>
+      </c>
+      <c r="Y9">
+        <v>0.1165961109732054</v>
+      </c>
+      <c r="Z9">
+        <v>0.7642511470052166</v>
+      </c>
+      <c r="AA9">
+        <v>0.1718063746220368</v>
+      </c>
+      <c r="AB9">
+        <v>0.05888507772738593</v>
+      </c>
+      <c r="AC9">
+        <v>0.1129212968946509</v>
+      </c>
+      <c r="AD9">
+        <v>7.64</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>7.64</v>
+      </c>
+      <c r="AG9">
+        <v>-43.06</v>
+      </c>
+      <c r="AH9">
+        <v>0.01825829270624223</v>
+      </c>
+      <c r="AI9">
+        <v>0.02756729450819081</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.117093598738239</v>
+      </c>
+      <c r="AK9">
+        <v>-0.1901607489842784</v>
+      </c>
+      <c r="AL9">
+        <v>0.628</v>
+      </c>
+      <c r="AM9">
+        <v>-5.052</v>
+      </c>
+      <c r="AN9">
+        <v>0.1948979591836734</v>
+      </c>
+      <c r="AO9">
+        <v>52.07006369426752</v>
+      </c>
+      <c r="AP9">
+        <v>-1.098469387755102</v>
+      </c>
+      <c r="AQ9">
+        <v>-6.47268408551069</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Indos SA (WSE:INS)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.05889999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="G10">
+        <v>0.7845188284518828</v>
+      </c>
+      <c r="H10">
+        <v>0.7845188284518828</v>
+      </c>
+      <c r="I10">
+        <v>0.6631799163179916</v>
+      </c>
+      <c r="J10">
+        <v>0.5117829222638185</v>
+      </c>
+      <c r="K10">
+        <v>1.18</v>
+      </c>
+      <c r="L10">
+        <v>0.2468619246861924</v>
+      </c>
+      <c r="M10">
+        <v>1.36</v>
+      </c>
+      <c r="N10">
+        <v>0.2155309033280507</v>
+      </c>
+      <c r="O10">
+        <v>1.152542372881356</v>
+      </c>
+      <c r="P10">
+        <v>1.36</v>
+      </c>
+      <c r="Q10">
+        <v>0.2155309033280507</v>
+      </c>
+      <c r="R10">
+        <v>1.152542372881356</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.1370499419279907</v>
+      </c>
+      <c r="X10">
+        <v>0.07499137088518554</v>
+      </c>
+      <c r="Y10">
+        <v>0.06205857104280518</v>
+      </c>
+      <c r="Z10">
+        <v>0.2726754135767256</v>
+      </c>
+      <c r="AA10">
+        <v>0.1395506199897919</v>
+      </c>
+      <c r="AB10">
+        <v>0.06208798426029732</v>
+      </c>
+      <c r="AC10">
+        <v>0.07746263572949461</v>
+      </c>
+      <c r="AD10">
+        <v>9.6</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>9.6</v>
+      </c>
+      <c r="AG10">
+        <v>9.6</v>
+      </c>
+      <c r="AH10">
+        <v>0.6033940917661847</v>
+      </c>
+      <c r="AI10">
+        <v>0.5109100585417775</v>
+      </c>
+      <c r="AJ10">
+        <v>0.6033940917661847</v>
+      </c>
+      <c r="AK10">
+        <v>0.5109100585417775</v>
+      </c>
+      <c r="AL10">
+        <v>1.02</v>
+      </c>
+      <c r="AM10">
+        <v>0.988</v>
+      </c>
+      <c r="AN10">
+        <v>2.891566265060241</v>
+      </c>
+      <c r="AO10">
+        <v>3.107843137254902</v>
+      </c>
+      <c r="AP10">
+        <v>2.891566265060241</v>
+      </c>
+      <c r="AQ10">
+        <v>3.208502024291498</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kredyt Inkaso S.A. (WSE:KRI)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.13</v>
+      </c>
+      <c r="G11">
+        <v>0.4957575757575757</v>
+      </c>
+      <c r="H11">
+        <v>0.4909090909090909</v>
+      </c>
+      <c r="I11">
+        <v>0.4560606060606061</v>
+      </c>
+      <c r="J11">
+        <v>0.2923785803237858</v>
+      </c>
+      <c r="K11">
+        <v>3.88</v>
+      </c>
+      <c r="L11">
+        <v>0.05878787878787878</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>17.3</v>
+      </c>
+      <c r="V11">
+        <v>0.287375415282392</v>
+      </c>
+      <c r="W11">
+        <v>0.0484394506866417</v>
+      </c>
+      <c r="X11">
+        <v>0.0796561159251116</v>
+      </c>
+      <c r="Y11">
+        <v>-0.0312166652384699</v>
+      </c>
+      <c r="Z11">
+        <v>0.4148595134829342</v>
+      </c>
+      <c r="AA11">
+        <v>0.1212960355859568</v>
+      </c>
+      <c r="AB11">
+        <v>0.0610605521477587</v>
+      </c>
+      <c r="AC11">
+        <v>0.0602354834381981</v>
+      </c>
+      <c r="AD11">
+        <v>118.1</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>118.1</v>
+      </c>
+      <c r="AG11">
+        <v>100.8</v>
+      </c>
+      <c r="AH11">
+        <v>0.6623667975322489</v>
+      </c>
+      <c r="AI11">
+        <v>0.5573383671543181</v>
+      </c>
+      <c r="AJ11">
+        <v>0.6260869565217391</v>
+      </c>
+      <c r="AK11">
+        <v>0.5179856115107914</v>
+      </c>
+      <c r="AL11">
+        <v>13.1</v>
+      </c>
+      <c r="AM11">
+        <v>12.143</v>
+      </c>
+      <c r="AN11">
+        <v>3.78525641025641</v>
+      </c>
+      <c r="AO11">
+        <v>2.297709923664122</v>
+      </c>
+      <c r="AP11">
+        <v>3.230769230769231</v>
+      </c>
+      <c r="AQ11">
+        <v>2.478794367125093</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>mPay S.A. (WSE:MPY)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.287</v>
+      </c>
+      <c r="G12">
+        <v>0.04544419134396356</v>
+      </c>
+      <c r="H12">
+        <v>0.02813211845102506</v>
+      </c>
+      <c r="I12">
+        <v>0.03337129840546697</v>
+      </c>
+      <c r="J12">
+        <v>0.02808475608380884</v>
+      </c>
+      <c r="K12">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="L12">
+        <v>0.009681093394077449</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.02309782608695652</v>
+      </c>
+      <c r="X12">
+        <v>0.06104509693283117</v>
+      </c>
+      <c r="Y12">
+        <v>-0.03794727084587464</v>
+      </c>
+      <c r="Z12">
+        <v>2.338215712383488</v>
+      </c>
+      <c r="AA12">
+        <v>0.06566821795361959</v>
+      </c>
+      <c r="AB12">
+        <v>0.05943693725639897</v>
+      </c>
+      <c r="AC12">
+        <v>0.00623128069722062</v>
+      </c>
+      <c r="AD12">
+        <v>1.04</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1.04</v>
+      </c>
+      <c r="AG12">
+        <v>1.04</v>
+      </c>
+      <c r="AH12">
+        <v>0.1699346405228758</v>
+      </c>
+      <c r="AI12">
+        <v>0.2153209109730849</v>
+      </c>
+      <c r="AJ12">
+        <v>0.1699346405228758</v>
+      </c>
+      <c r="AK12">
+        <v>0.2153209109730849</v>
+      </c>
+      <c r="AL12">
+        <v>0.201</v>
+      </c>
+      <c r="AM12">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="AN12">
+        <v>3.2</v>
+      </c>
+      <c r="AO12">
+        <v>1.45771144278607</v>
+      </c>
+      <c r="AP12">
+        <v>3.2</v>
+      </c>
+      <c r="AQ12">
+        <v>3.329545454545454</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AKCEPT Finance S.A. (WSE:AFC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.422</v>
+      </c>
+      <c r="G13">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="H13">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="I13">
+        <v>0.4871794871794872</v>
+      </c>
+      <c r="J13">
+        <v>0.4871794871794872</v>
+      </c>
+      <c r="K13">
+        <v>-0.12</v>
+      </c>
+      <c r="L13">
+        <v>-3.076923076923077</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>-3.636363636363636</v>
+      </c>
+      <c r="X13">
+        <v>0.101147778342101</v>
+      </c>
+      <c r="Y13">
+        <v>-3.737511414705737</v>
+      </c>
+      <c r="Z13">
+        <v>0.02760084925690022</v>
+      </c>
+      <c r="AA13">
+        <v>0.01344656758669498</v>
+      </c>
+      <c r="AB13">
+        <v>0.06313239061558895</v>
+      </c>
+      <c r="AC13">
+        <v>-0.04968582302889397</v>
+      </c>
+      <c r="AD13">
+        <v>0.87</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0.87</v>
+      </c>
+      <c r="AG13">
+        <v>0.87</v>
+      </c>
+      <c r="AH13">
+        <v>0.7996323529411764</v>
+      </c>
+      <c r="AI13">
+        <v>1.104060913705584</v>
+      </c>
+      <c r="AJ13">
+        <v>0.7996323529411764</v>
+      </c>
+      <c r="AK13">
+        <v>1.104060913705584</v>
+      </c>
+      <c r="AL13">
+        <v>0.154</v>
+      </c>
+      <c r="AM13">
+        <v>0.154</v>
+      </c>
+      <c r="AN13">
+        <v>41.42857142857142</v>
+      </c>
+      <c r="AO13">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="AP13">
+        <v>41.42857142857142</v>
+      </c>
+      <c r="AQ13">
+        <v>0.1233766233766234</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NWAI Dom Maklerski S.A. (WSE:NWA)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.327</v>
+      </c>
+      <c r="E14">
+        <v>2.11</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1.86</v>
+      </c>
+      <c r="L14">
+        <v>0.2892690513219285</v>
+      </c>
+      <c r="M14">
+        <v>0.846</v>
+      </c>
+      <c r="N14">
+        <v>0.09825783972125436</v>
+      </c>
+      <c r="O14">
+        <v>0.4548387096774193</v>
+      </c>
+      <c r="P14">
+        <v>0.846</v>
+      </c>
+      <c r="Q14">
+        <v>0.09825783972125436</v>
+      </c>
+      <c r="R14">
+        <v>0.4548387096774193</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>39.7</v>
+      </c>
+      <c r="V14">
+        <v>4.610917537746807</v>
+      </c>
+      <c r="W14">
+        <v>0.4161073825503356</v>
+      </c>
+      <c r="X14">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="Y14">
+        <v>0.357230742603898</v>
+      </c>
+      <c r="Z14">
+        <v>2.074193548387097</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05887663994643765</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>-39.7</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>1.276937922161467</v>
+      </c>
+      <c r="AK14">
+        <v>1.192908653846154</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1.16</v>
+      </c>
+      <c r="AQ14">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wierzyciel S.A. (WSE:WRL)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.152</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-0.078</v>
+      </c>
+      <c r="L15">
+        <v>-0.1084840055632823</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>-0.04285714285714286</v>
+      </c>
+      <c r="X15">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="Y15">
+        <v>-0.1017337828035805</v>
+      </c>
+      <c r="Z15">
+        <v>0.395054945054945</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05887663994643765</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05887663994643765</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-0.008</v>
+      </c>
+      <c r="AQ15">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IDM Spólka Akcyjna (WSE:IDM)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>-0.157</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0.003</v>
+      </c>
+      <c r="V16">
+        <v>0.0004587155963302753</v>
+      </c>
+      <c r="W16">
+        <v>-1.006410256410256</v>
+      </c>
+      <c r="X16">
+        <v>0.05943053762196703</v>
+      </c>
+      <c r="Y16">
+        <v>-1.065840794032223</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05904049055471921</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05904049055471921</v>
+      </c>
+      <c r="AD16">
+        <v>0.342</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0.342</v>
+      </c>
+      <c r="AG16">
+        <v>0.339</v>
+      </c>
+      <c r="AH16">
+        <v>0.04969485614646905</v>
+      </c>
+      <c r="AI16">
+        <v>0.9421487603305785</v>
+      </c>
+      <c r="AJ16">
+        <v>0.04928041866550371</v>
+      </c>
+      <c r="AK16">
+        <v>0.9416666666666667</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-0.77</v>
+      </c>
+      <c r="AQ16">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pragma Inkaso S.A. (WSE:PRI)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.347</v>
+      </c>
+      <c r="G17">
+        <v>-0.1516949152542373</v>
+      </c>
+      <c r="H17">
+        <v>-0.1516949152542373</v>
+      </c>
+      <c r="I17">
+        <v>-0.1889830508474576</v>
+      </c>
+      <c r="J17">
+        <v>-0.1889830508474576</v>
+      </c>
+      <c r="K17">
+        <v>-0.183</v>
+      </c>
+      <c r="L17">
+        <v>-0.1550847457627119</v>
+      </c>
+      <c r="M17">
+        <v>0.003</v>
+      </c>
+      <c r="N17">
+        <v>0.0008955223880597015</v>
+      </c>
+      <c r="O17">
+        <v>-0.01639344262295082</v>
+      </c>
+      <c r="P17">
+        <v>0.003</v>
+      </c>
+      <c r="Q17">
+        <v>0.0008955223880597015</v>
+      </c>
+      <c r="R17">
+        <v>-0.01639344262295082</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0.786</v>
+      </c>
+      <c r="V17">
+        <v>0.2346268656716418</v>
+      </c>
+      <c r="W17">
+        <v>-0.03446327683615819</v>
+      </c>
+      <c r="X17">
+        <v>0.06104880646315233</v>
+      </c>
+      <c r="Y17">
+        <v>-0.09551208329931052</v>
+      </c>
+      <c r="Z17">
+        <v>0.2226415094339623</v>
+      </c>
+      <c r="AA17">
+        <v>-0.04207547169811321</v>
+      </c>
+      <c r="AB17">
+        <v>0.05978233877598877</v>
+      </c>
+      <c r="AC17">
+        <v>-0.101857810474102</v>
+      </c>
+      <c r="AD17">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="AG17">
+        <v>-0.09899999999999998</v>
+      </c>
+      <c r="AH17">
+        <v>0.1701758731731484</v>
+      </c>
+      <c r="AI17">
+        <v>0.1077309079504469</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.03045216856351891</v>
+      </c>
+      <c r="AK17">
+        <v>-0.01770702915399749</v>
+      </c>
+      <c r="AL17">
+        <v>0.041</v>
+      </c>
+      <c r="AM17">
+        <v>0.016</v>
+      </c>
+      <c r="AN17">
+        <v>-12.72222222222222</v>
+      </c>
+      <c r="AO17">
+        <v>-5.439024390243902</v>
+      </c>
+      <c r="AP17">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="AQ17">
+        <v>-13.9375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LexBono S.A. (WSE:LXB)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.287</v>
+      </c>
+      <c r="G18">
+        <v>-0.6020942408376964</v>
+      </c>
+      <c r="H18">
+        <v>-0.6020942408376964</v>
+      </c>
+      <c r="I18">
+        <v>-0.6649214659685864</v>
+      </c>
+      <c r="J18">
+        <v>-0.6649214659685864</v>
+      </c>
+      <c r="K18">
+        <v>-0.155</v>
+      </c>
+      <c r="L18">
+        <v>-0.4057591623036649</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0.007</v>
+      </c>
+      <c r="V18">
+        <v>0.01605504587155963</v>
+      </c>
+      <c r="W18">
+        <v>-0.5032467532467533</v>
+      </c>
+      <c r="X18">
+        <v>0.09070146253167846</v>
+      </c>
+      <c r="Y18">
+        <v>-0.5939482157784317</v>
+      </c>
+      <c r="Z18">
+        <v>0.2495101241018942</v>
+      </c>
+      <c r="AA18">
+        <v>-0.1659046374918354</v>
+      </c>
+      <c r="AB18">
+        <v>0.06286976466746039</v>
+      </c>
+      <c r="AC18">
+        <v>-0.2287744021592958</v>
+      </c>
+      <c r="AD18">
+        <v>1.31</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>1.31</v>
+      </c>
+      <c r="AG18">
+        <v>1.303</v>
+      </c>
+      <c r="AH18">
+        <v>0.7502863688430699</v>
+      </c>
+      <c r="AI18">
+        <v>0.8899456521739131</v>
+      </c>
+      <c r="AJ18">
+        <v>0.7492811960897068</v>
+      </c>
+      <c r="AK18">
+        <v>0.8894197952218431</v>
+      </c>
+      <c r="AL18">
+        <v>0.132</v>
+      </c>
+      <c r="AM18">
+        <v>0.132</v>
+      </c>
+      <c r="AO18">
+        <v>-1.924242424242424</v>
+      </c>
+      <c r="AQ18">
+        <v>-1.924242424242424</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fundusz Hipoteczny DOM S.A. (WSE:FHD)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>-2.03</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.451</v>
+      </c>
+      <c r="V19">
+        <v>0.03089041095890411</v>
+      </c>
+      <c r="W19">
+        <v>-0.8826086956521739</v>
+      </c>
+      <c r="X19">
+        <v>0.05913563802680144</v>
+      </c>
+      <c r="Y19">
+        <v>-0.9417443336789754</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>-1</v>
+      </c>
+      <c r="AB19">
+        <v>0.05900367089507347</v>
+      </c>
+      <c r="AC19">
+        <v>-1.059003670895073</v>
+      </c>
+      <c r="AD19">
+        <v>0.357</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0.357</v>
+      </c>
+      <c r="AG19">
+        <v>-0.09400000000000003</v>
+      </c>
+      <c r="AH19">
+        <v>0.02386842281206124</v>
+      </c>
+      <c r="AI19">
+        <v>0.5433789954337899</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.006480077209430582</v>
+      </c>
+      <c r="AK19">
+        <v>-0.4563106796116507</v>
+      </c>
+      <c r="AL19">
+        <v>0.839</v>
+      </c>
+      <c r="AM19">
+        <v>0.83</v>
+      </c>
+      <c r="AN19">
+        <v>-0.1222602739726027</v>
+      </c>
+      <c r="AO19">
+        <v>-3.528009535160906</v>
+      </c>
+      <c r="AP19">
+        <v>0.03219178082191782</v>
+      </c>
+      <c r="AQ19">
+        <v>-3.566265060240964</v>
       </c>
     </row>
   </sheetData>
